--- a/data/published/MEPS_Quota_Update_latest.xlsx
+++ b/data/published/MEPS_Quota_Update_latest.xlsx
@@ -1619,8 +1619,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{ABB843BB-6D4C-413D-9459-234F25C2F640}" name="EU_Quotas4" displayName="EU_Quotas4" ref="A15:G297" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A15:G297" xr:uid="{E868E768-6237-458A-90D6-C15D3AA0A2D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{ABB843BB-6D4C-413D-9459-234F25C2F640}" name="EU_Quotas4" displayName="EU_Quotas4" ref="A15:G298" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A15:G298" xr:uid="{E868E768-6237-458A-90D6-C15D3AA0A2D9}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{B473FDE6-67DB-44AB-82D0-62A9576B1E19}" name="Quota Category" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{99A5909C-6233-411A-8FED-2CA191C65C68}" name="Country" dataDxfId="14"/>
@@ -2114,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0945755B-B1DA-4C41-B8AC-7AFC3C5D71DF}">
-  <dimension ref="A1:G297"/>
+  <dimension ref="A1:G298"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="64.140625" style="1" customWidth="1"/>
@@ -2286,23 +2286,23 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C17" s="22">
-        <v>137884.78</v>
+        <v>69730.64</v>
       </c>
       <c r="D17" s="22">
-        <v>0.64</v>
+        <v>1957.45</v>
       </c>
       <c r="E17" s="24">
-        <v>0.0</v>
+        <v>0.0281</v>
       </c>
       <c r="F17" s="22">
-        <v>137884.14</v>
+        <v>67773.19</v>
       </c>
       <c r="G17" s="24">
-        <v>1.0</v>
+        <v>0.9719</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17.45">
@@ -2340,23 +2340,23 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C19" s="22">
-        <v>69730.64</v>
+        <v>160573.74</v>
       </c>
       <c r="D19" s="22">
-        <v>1957.45</v>
+        <v>160573.74</v>
       </c>
       <c r="E19" s="24">
-        <v>0.0281</v>
+        <v>1.0</v>
       </c>
       <c r="F19" s="22">
-        <v>67773.19</v>
+        <v>0.0</v>
       </c>
       <c r="G19" s="24">
-        <v>0.9719</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17.45">
@@ -2367,23 +2367,23 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C20" s="22">
-        <v>160573.74</v>
+        <v>137884.78</v>
       </c>
       <c r="D20" s="22">
-        <v>160573.74</v>
+        <v>0.64</v>
       </c>
       <c r="E20" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F20" s="22">
-        <v>0.0</v>
+        <v>137884.14</v>
       </c>
       <c r="G20" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="17.45">
@@ -2394,23 +2394,23 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C21" s="22">
-        <v>115457.52</v>
+        <v>103743.08</v>
       </c>
       <c r="D21" s="22">
-        <v>15918.51</v>
+        <v>20219.69</v>
       </c>
       <c r="E21" s="24">
-        <v>0.1379</v>
+        <v>0.1949</v>
       </c>
       <c r="F21" s="22">
-        <v>99539.01</v>
+        <v>83523.4</v>
       </c>
       <c r="G21" s="24">
-        <v>0.8621</v>
+        <v>0.8051</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="17.45">
@@ -2421,23 +2421,23 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C22" s="22">
-        <v>42512.75</v>
+        <v>115457.52</v>
       </c>
       <c r="D22" s="22">
-        <v>46.74</v>
+        <v>15918.51</v>
       </c>
       <c r="E22" s="24">
-        <v>0.0011</v>
+        <v>0.1379</v>
       </c>
       <c r="F22" s="22">
-        <v>42466.01</v>
+        <v>99539.01</v>
       </c>
       <c r="G22" s="24">
-        <v>0.9989</v>
+        <v>0.8621</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17.45">
@@ -2448,23 +2448,23 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C23" s="22">
-        <v>120920.56</v>
+        <v>64523.65</v>
       </c>
       <c r="D23" s="22">
-        <v>0.0</v>
+        <v>1088.82</v>
       </c>
       <c r="E23" s="24">
-        <v>0.0</v>
+        <v>0.0169</v>
       </c>
       <c r="F23" s="22">
-        <v>120920.56</v>
+        <v>63434.83</v>
       </c>
       <c r="G23" s="24">
-        <v>1.0</v>
+        <v>0.9831</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="17.45">
@@ -2502,23 +2502,23 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C25" s="22">
-        <v>64523.65</v>
+        <v>120920.56</v>
       </c>
       <c r="D25" s="22">
-        <v>1088.82</v>
+        <v>0.0</v>
       </c>
       <c r="E25" s="24">
-        <v>0.0169</v>
+        <v>0.0</v>
       </c>
       <c r="F25" s="22">
-        <v>63434.83</v>
+        <v>120920.56</v>
       </c>
       <c r="G25" s="24">
-        <v>0.9831</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="17.45">
@@ -2529,23 +2529,23 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C26" s="22">
-        <v>38481.14</v>
+        <v>42512.75</v>
       </c>
       <c r="D26" s="22">
-        <v>226.31</v>
+        <v>46.74</v>
       </c>
       <c r="E26" s="24">
-        <v>0.0059</v>
+        <v>0.0011</v>
       </c>
       <c r="F26" s="22">
-        <v>38254.83</v>
+        <v>42466.01</v>
       </c>
       <c r="G26" s="24">
-        <v>0.9941</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17.45">
@@ -2556,23 +2556,23 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C27" s="22">
-        <v>5472.5</v>
+        <v>31834.46</v>
       </c>
       <c r="D27" s="22">
-        <v>6.29</v>
+        <v>16318.95</v>
       </c>
       <c r="E27" s="24">
-        <v>0.0011</v>
+        <v>0.5126</v>
       </c>
       <c r="F27" s="22">
-        <v>5466.21</v>
+        <v>15515.51</v>
       </c>
       <c r="G27" s="24">
-        <v>0.9989</v>
+        <v>0.4874</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="17.45">
@@ -2583,23 +2583,23 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C28" s="22">
-        <v>9545.08</v>
+        <v>38481.14</v>
       </c>
       <c r="D28" s="22">
-        <v>0.0</v>
+        <v>226.31</v>
       </c>
       <c r="E28" s="24">
-        <v>0.0</v>
+        <v>0.0059</v>
       </c>
       <c r="F28" s="22">
-        <v>9545.08</v>
+        <v>38254.83</v>
       </c>
       <c r="G28" s="24">
-        <v>1.0</v>
+        <v>0.9941</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17.45">
@@ -2610,23 +2610,23 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C29" s="22">
-        <v>31834.46</v>
+        <v>11830.05</v>
       </c>
       <c r="D29" s="22">
-        <v>16318.95</v>
+        <v>0.0</v>
       </c>
       <c r="E29" s="24">
-        <v>0.5126</v>
+        <v>0.0</v>
       </c>
       <c r="F29" s="22">
-        <v>15515.51</v>
+        <v>11830.05</v>
       </c>
       <c r="G29" s="24">
-        <v>0.4874</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17.45">
@@ -2637,11 +2637,11 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C30" s="22">
-        <v>2377.67</v>
+        <v>9545.08</v>
       </c>
       <c r="D30" s="22">
         <v>0.0</v>
@@ -2650,7 +2650,7 @@
         <v>0.0</v>
       </c>
       <c r="F30" s="22">
-        <v>2377.67</v>
+        <v>9545.08</v>
       </c>
       <c r="G30" s="24">
         <v>1.0</v>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C31" s="22">
-        <v>11830.05</v>
+        <v>5472.5</v>
       </c>
       <c r="D31" s="22">
-        <v>0.0</v>
+        <v>6.29</v>
       </c>
       <c r="E31" s="24">
-        <v>0.0</v>
+        <v>0.0011</v>
       </c>
       <c r="F31" s="22">
-        <v>11830.05</v>
+        <v>5466.21</v>
       </c>
       <c r="G31" s="24">
-        <v>1.0</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17.45">
@@ -2691,23 +2691,23 @@
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C32" s="22">
-        <v>3531.91</v>
+        <v>5564.01</v>
       </c>
       <c r="D32" s="22">
-        <v>177.59</v>
+        <v>5564.01</v>
       </c>
       <c r="E32" s="24">
-        <v>0.0503</v>
+        <v>1.0</v>
       </c>
       <c r="F32" s="22">
-        <v>3354.32</v>
+        <v>0.0</v>
       </c>
       <c r="G32" s="24">
-        <v>0.9497</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17.45">
@@ -2718,23 +2718,23 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C33" s="22">
-        <v>5564.01</v>
+        <v>4271.87</v>
       </c>
       <c r="D33" s="22">
-        <v>5564.01</v>
+        <v>2172.04</v>
       </c>
       <c r="E33" s="24">
-        <v>1.0</v>
+        <v>0.5085</v>
       </c>
       <c r="F33" s="22">
-        <v>0.0</v>
+        <v>2099.83</v>
       </c>
       <c r="G33" s="24">
-        <v>0.0</v>
+        <v>0.4915</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17.45">
@@ -2745,50 +2745,50 @@
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C34" s="22">
-        <v>4271.87</v>
+        <v>2377.67</v>
       </c>
       <c r="D34" s="22">
-        <v>2172.04</v>
+        <v>0.0</v>
       </c>
       <c r="E34" s="24">
-        <v>0.5085</v>
+        <v>0.0</v>
       </c>
       <c r="F34" s="22">
-        <v>2099.83</v>
+        <v>2377.67</v>
       </c>
       <c r="G34" s="24">
-        <v>0.4915</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="17.45">
       <c r="A35" s="21" t="inlineStr">
         <is>
-          <t>Non Alloy and Other Alloy Hot Rolled Sheets and Strips - 1.B</t>
+          <t>Non Alloy and Other Alloy Hot Rolled Sheets and Strips - 1.A</t>
         </is>
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C35" s="22">
-        <v>526.03</v>
+        <v>3531.91</v>
       </c>
       <c r="D35" s="22">
-        <v>25.31</v>
+        <v>177.59</v>
       </c>
       <c r="E35" s="24">
-        <v>0.0481</v>
+        <v>0.0503</v>
       </c>
       <c r="F35" s="22">
-        <v>500.72</v>
+        <v>3354.32</v>
       </c>
       <c r="G35" s="24">
-        <v>0.9519</v>
+        <v>0.9497</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="17.45">
@@ -2799,23 +2799,23 @@
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C36" s="22">
-        <v>106.52</v>
+        <v>127.34</v>
       </c>
       <c r="D36" s="22">
-        <v>0.0</v>
+        <v>83.66</v>
       </c>
       <c r="E36" s="24">
-        <v>0.0</v>
+        <v>0.657</v>
       </c>
       <c r="F36" s="22">
-        <v>106.52</v>
+        <v>43.68</v>
       </c>
       <c r="G36" s="24">
-        <v>1.0</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="17.45">
@@ -2826,23 +2826,23 @@
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C37" s="22">
-        <v>127.34</v>
+        <v>526.03</v>
       </c>
       <c r="D37" s="22">
-        <v>83.66</v>
+        <v>25.31</v>
       </c>
       <c r="E37" s="24">
-        <v>0.657</v>
+        <v>0.0481</v>
       </c>
       <c r="F37" s="22">
-        <v>43.68</v>
+        <v>500.72</v>
       </c>
       <c r="G37" s="24">
-        <v>0.343</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17.45">
@@ -2880,11 +2880,11 @@
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C39" s="22">
-        <v>44.89</v>
+        <v>35.59</v>
       </c>
       <c r="D39" s="22">
         <v>0.0</v>
@@ -2893,7 +2893,7 @@
         <v>0.0</v>
       </c>
       <c r="F39" s="22">
-        <v>44.89</v>
+        <v>35.59</v>
       </c>
       <c r="G39" s="24">
         <v>1.0</v>
@@ -2907,11 +2907,11 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C40" s="22">
-        <v>35.59</v>
+        <v>106.52</v>
       </c>
       <c r="D40" s="22">
         <v>0.0</v>
@@ -2920,7 +2920,7 @@
         <v>0.0</v>
       </c>
       <c r="F40" s="22">
-        <v>35.59</v>
+        <v>106.52</v>
       </c>
       <c r="G40" s="24">
         <v>1.0</v>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C41" s="22">
-        <v>60.94</v>
+        <v>44.89</v>
       </c>
       <c r="D41" s="22">
         <v>0.0</v>
@@ -2947,7 +2947,7 @@
         <v>0.0</v>
       </c>
       <c r="F41" s="22">
-        <v>60.94</v>
+        <v>44.89</v>
       </c>
       <c r="G41" s="24">
         <v>1.0</v>
@@ -2961,50 +2961,50 @@
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C42" s="22">
-        <v>33586.54</v>
+        <v>67493.58</v>
       </c>
       <c r="D42" s="22">
-        <v>19.8</v>
+        <v>2176.23</v>
       </c>
       <c r="E42" s="24">
-        <v>0.0006</v>
+        <v>0.0322</v>
       </c>
       <c r="F42" s="22">
-        <v>33566.74</v>
+        <v>65317.35</v>
       </c>
       <c r="G42" s="24">
-        <v>0.9994</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="17.45">
       <c r="A43" s="21" t="inlineStr">
         <is>
-          <t>Non Alloy and Other Alloy Cold Rolled Sheets - 2</t>
+          <t>Non Alloy and Other Alloy Hot Rolled Sheets and Strips - 1.B</t>
         </is>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C43" s="22">
-        <v>19834.63</v>
+        <v>60.94</v>
       </c>
       <c r="D43" s="22">
-        <v>22.61</v>
+        <v>0.0</v>
       </c>
       <c r="E43" s="24">
-        <v>0.0011</v>
+        <v>0.0</v>
       </c>
       <c r="F43" s="22">
-        <v>19812.02</v>
+        <v>60.94</v>
       </c>
       <c r="G43" s="24">
-        <v>0.9989</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="17.45">
@@ -3015,23 +3015,23 @@
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C44" s="22">
-        <v>60152.91</v>
+        <v>63652.67</v>
       </c>
       <c r="D44" s="22">
-        <v>17956.34</v>
+        <v>23511.08</v>
       </c>
       <c r="E44" s="24">
-        <v>0.2985</v>
+        <v>0.3694</v>
       </c>
       <c r="F44" s="22">
-        <v>42196.57</v>
+        <v>40141.59</v>
       </c>
       <c r="G44" s="24">
-        <v>0.7015</v>
+        <v>0.6306</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17.45">
@@ -3042,23 +3042,23 @@
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C45" s="22">
-        <v>67493.58</v>
+        <v>33586.54</v>
       </c>
       <c r="D45" s="22">
-        <v>2176.23</v>
+        <v>19.8</v>
       </c>
       <c r="E45" s="24">
-        <v>0.0322</v>
+        <v>0.0006</v>
       </c>
       <c r="F45" s="22">
-        <v>65317.35</v>
+        <v>33566.74</v>
       </c>
       <c r="G45" s="24">
-        <v>0.9678</v>
+        <v>0.9994</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17.45">
@@ -3069,23 +3069,23 @@
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C46" s="22">
-        <v>63652.67</v>
+        <v>19834.63</v>
       </c>
       <c r="D46" s="22">
-        <v>23511.08</v>
+        <v>22.61</v>
       </c>
       <c r="E46" s="24">
-        <v>0.3694</v>
+        <v>0.0011</v>
       </c>
       <c r="F46" s="22">
-        <v>40141.59</v>
+        <v>19812.02</v>
       </c>
       <c r="G46" s="24">
-        <v>0.6306</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="17.45">
@@ -3123,23 +3123,23 @@
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C48" s="22">
-        <v>26549.48</v>
+        <v>60152.91</v>
       </c>
       <c r="D48" s="22">
-        <v>1711.08</v>
+        <v>17956.34</v>
       </c>
       <c r="E48" s="24">
-        <v>0.0644</v>
+        <v>0.2985</v>
       </c>
       <c r="F48" s="22">
-        <v>24838.4</v>
+        <v>42196.57</v>
       </c>
       <c r="G48" s="24">
-        <v>0.9356</v>
+        <v>0.7015</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="17.45">
@@ -3177,23 +3177,23 @@
       </c>
       <c r="B50" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C50" s="22">
-        <v>745.65</v>
+        <v>26549.48</v>
       </c>
       <c r="D50" s="22">
-        <v>1.19</v>
+        <v>1711.08</v>
       </c>
       <c r="E50" s="24">
-        <v>0.0016</v>
+        <v>0.0644</v>
       </c>
       <c r="F50" s="22">
-        <v>744.46</v>
+        <v>24838.4</v>
       </c>
       <c r="G50" s="24">
-        <v>0.9984</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="17.45">
@@ -3231,77 +3231,77 @@
       </c>
       <c r="B52" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C52" s="22">
-        <v>21283.6</v>
+        <v>1294.54</v>
       </c>
       <c r="D52" s="22">
-        <v>25.96</v>
+        <v>343.64</v>
       </c>
       <c r="E52" s="24">
-        <v>0.0012</v>
+        <v>0.2654</v>
       </c>
       <c r="F52" s="22">
-        <v>21257.64</v>
+        <v>950.9</v>
       </c>
       <c r="G52" s="24">
-        <v>0.9988</v>
+        <v>0.7346</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="17.45">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>Non Alloy and Other Alloy Cold Rolled Sheets - 2</t>
+          <t>Electrical Sheets (other than GOES) - 3.A</t>
         </is>
       </c>
       <c r="B53" s="21" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C53" s="22">
-        <v>1294.54</v>
+        <v>77.95</v>
       </c>
       <c r="D53" s="22">
-        <v>343.64</v>
+        <v>0.0</v>
       </c>
       <c r="E53" s="24">
-        <v>0.2654</v>
+        <v>0.0</v>
       </c>
       <c r="F53" s="22">
-        <v>950.9</v>
+        <v>77.95</v>
       </c>
       <c r="G53" s="24">
-        <v>0.7346</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="17.45">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>Electrical Sheets (other than GOES) - 3.A</t>
+          <t>Non Alloy and Other Alloy Cold Rolled Sheets - 2</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C54" s="22">
-        <v>77.95</v>
+        <v>745.65</v>
       </c>
       <c r="D54" s="22">
-        <v>0.0</v>
+        <v>1.19</v>
       </c>
       <c r="E54" s="24">
-        <v>0.0</v>
+        <v>0.0016</v>
       </c>
       <c r="F54" s="22">
-        <v>77.95</v>
+        <v>744.46</v>
       </c>
       <c r="G54" s="24">
-        <v>1.0</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="17.45">
@@ -3339,11 +3339,11 @@
       </c>
       <c r="B56" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C56" s="22">
-        <v>7.27</v>
+        <v>19.56</v>
       </c>
       <c r="D56" s="22">
         <v>0.0</v>
@@ -3352,7 +3352,7 @@
         <v>0.0</v>
       </c>
       <c r="F56" s="22">
-        <v>7.27</v>
+        <v>19.56</v>
       </c>
       <c r="G56" s="24">
         <v>1.0</v>
@@ -3366,11 +3366,11 @@
       </c>
       <c r="B57" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C57" s="22">
-        <v>29.05</v>
+        <v>4.98</v>
       </c>
       <c r="D57" s="22">
         <v>0.0</v>
@@ -3379,7 +3379,7 @@
         <v>0.0</v>
       </c>
       <c r="F57" s="22">
-        <v>29.05</v>
+        <v>4.98</v>
       </c>
       <c r="G57" s="24">
         <v>1.0</v>
@@ -3393,11 +3393,11 @@
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C58" s="22">
-        <v>4.98</v>
+        <v>8.69</v>
       </c>
       <c r="D58" s="22">
         <v>0.0</v>
@@ -3406,7 +3406,7 @@
         <v>0.0</v>
       </c>
       <c r="F58" s="22">
-        <v>4.98</v>
+        <v>8.69</v>
       </c>
       <c r="G58" s="24">
         <v>1.0</v>
@@ -3420,11 +3420,11 @@
       </c>
       <c r="B59" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C59" s="22">
-        <v>8.69</v>
+        <v>29.05</v>
       </c>
       <c r="D59" s="22">
         <v>0.0</v>
@@ -3433,7 +3433,7 @@
         <v>0.0</v>
       </c>
       <c r="F59" s="22">
-        <v>8.69</v>
+        <v>29.05</v>
       </c>
       <c r="G59" s="24">
         <v>1.0</v>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C60" s="22">
-        <v>19.56</v>
+        <v>7.27</v>
       </c>
       <c r="D60" s="22">
         <v>0.0</v>
@@ -3460,7 +3460,7 @@
         <v>0.0</v>
       </c>
       <c r="F60" s="22">
-        <v>19.56</v>
+        <v>7.27</v>
       </c>
       <c r="G60" s="24">
         <v>1.0</v>
@@ -3469,19 +3469,19 @@
     <row r="61" spans="1:7" ht="17.45">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>Electrical Sheets (other than GOES) - 3.B</t>
+          <t>Electrical Sheets (other than GOES) - 3.A</t>
         </is>
       </c>
       <c r="B61" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C61" s="22">
-        <v>11837.81</v>
+        <v>5.43</v>
       </c>
       <c r="D61" s="22">
-        <v>11837.81</v>
+        <v>5.43</v>
       </c>
       <c r="E61" s="24">
         <v>1.0</v>
@@ -3496,7 +3496,7 @@
     <row r="62" spans="1:7" ht="17.45">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>Electrical Sheets (other than GOES) - 3.A</t>
+          <t>Non Alloy and Other Alloy Cold Rolled Sheets - 2</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
@@ -3505,19 +3505,19 @@
         </is>
       </c>
       <c r="C62" s="22">
-        <v>5.43</v>
+        <v>21283.6</v>
       </c>
       <c r="D62" s="22">
-        <v>5.43</v>
+        <v>25.96</v>
       </c>
       <c r="E62" s="24">
-        <v>1.0</v>
+        <v>0.0012</v>
       </c>
       <c r="F62" s="22">
-        <v>0.0</v>
+        <v>21257.64</v>
       </c>
       <c r="G62" s="24">
-        <v>0.0</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17.45">
@@ -3528,23 +3528,23 @@
       </c>
       <c r="B63" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C63" s="22">
-        <v>15495.38</v>
+        <v>5166.66</v>
       </c>
       <c r="D63" s="22">
-        <v>16.98</v>
+        <v>0.0</v>
       </c>
       <c r="E63" s="24">
-        <v>0.0011</v>
+        <v>0.0</v>
       </c>
       <c r="F63" s="22">
-        <v>15478.4</v>
+        <v>5166.66</v>
       </c>
       <c r="G63" s="24">
-        <v>0.9989</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="17.45">
@@ -3555,23 +3555,23 @@
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C64" s="22">
-        <v>5166.66</v>
+        <v>11837.81</v>
       </c>
       <c r="D64" s="22">
-        <v>0.0</v>
+        <v>11837.81</v>
       </c>
       <c r="E64" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F64" s="22">
-        <v>5166.66</v>
+        <v>0.0</v>
       </c>
       <c r="G64" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="17.45">
@@ -3609,50 +3609,50 @@
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C66" s="22">
-        <v>6925.39</v>
+        <v>15495.38</v>
       </c>
       <c r="D66" s="22">
-        <v>0.0</v>
+        <v>16.98</v>
       </c>
       <c r="E66" s="24">
-        <v>0.0</v>
+        <v>0.0011</v>
       </c>
       <c r="F66" s="22">
-        <v>6925.39</v>
+        <v>15478.4</v>
       </c>
       <c r="G66" s="24">
-        <v>1.0</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="17.45">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>Metallic Coated Sheets - 4.A</t>
+          <t>Electrical Sheets (other than GOES) - 3.B</t>
         </is>
       </c>
       <c r="B67" s="21" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C67" s="22">
-        <v>117496.92</v>
+        <v>1478.75</v>
       </c>
       <c r="D67" s="22">
-        <v>15271.57</v>
+        <v>0.0</v>
       </c>
       <c r="E67" s="24">
-        <v>0.13</v>
+        <v>0.0</v>
       </c>
       <c r="F67" s="22">
-        <v>102225.35</v>
+        <v>1478.75</v>
       </c>
       <c r="G67" s="24">
-        <v>0.87</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17.45">
@@ -3663,11 +3663,11 @@
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C68" s="22">
-        <v>1478.75</v>
+        <v>6925.39</v>
       </c>
       <c r="D68" s="22">
         <v>0.0</v>
@@ -3676,7 +3676,7 @@
         <v>0.0</v>
       </c>
       <c r="F68" s="22">
-        <v>1478.75</v>
+        <v>6925.39</v>
       </c>
       <c r="G68" s="24">
         <v>1.0</v>
@@ -3712,28 +3712,28 @@
     <row r="70" spans="1:7" ht="17.45">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>Metallic Coated Sheets - 4.A</t>
+          <t>Electrical Sheets (other than GOES) - 3.B</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C70" s="22">
-        <v>33783.39</v>
+        <v>554.14</v>
       </c>
       <c r="D70" s="22">
-        <v>17016.88</v>
+        <v>0.0</v>
       </c>
       <c r="E70" s="24">
-        <v>0.5037</v>
+        <v>0.0</v>
       </c>
       <c r="F70" s="22">
-        <v>16766.51</v>
+        <v>554.14</v>
       </c>
       <c r="G70" s="24">
-        <v>0.4963</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17.45">
@@ -3744,23 +3744,23 @@
       </c>
       <c r="B71" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C71" s="22">
-        <v>63925.33</v>
+        <v>117496.92</v>
       </c>
       <c r="D71" s="22">
-        <v>63925.33</v>
+        <v>15271.57</v>
       </c>
       <c r="E71" s="24">
-        <v>1.0</v>
+        <v>0.13</v>
       </c>
       <c r="F71" s="22">
-        <v>0.0</v>
+        <v>102225.35</v>
       </c>
       <c r="G71" s="24">
-        <v>0.0</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="17.45">
@@ -3771,23 +3771,23 @@
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C72" s="22">
-        <v>58295.85</v>
+        <v>33783.39</v>
       </c>
       <c r="D72" s="22">
-        <v>223.45</v>
+        <v>17016.88</v>
       </c>
       <c r="E72" s="24">
-        <v>0.0038</v>
+        <v>0.5037</v>
       </c>
       <c r="F72" s="22">
-        <v>58072.4</v>
+        <v>16766.51</v>
       </c>
       <c r="G72" s="24">
-        <v>0.9962</v>
+        <v>0.4963</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17.45">
@@ -3798,23 +3798,23 @@
       </c>
       <c r="B73" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C73" s="22">
-        <v>26119.93</v>
+        <v>63925.33</v>
       </c>
       <c r="D73" s="22">
-        <v>10595.37</v>
+        <v>63925.33</v>
       </c>
       <c r="E73" s="24">
-        <v>0.4056</v>
+        <v>1.0</v>
       </c>
       <c r="F73" s="22">
-        <v>15524.56</v>
+        <v>0.0</v>
       </c>
       <c r="G73" s="24">
-        <v>0.5944</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="17.45">
@@ -3825,23 +3825,23 @@
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C74" s="22">
-        <v>33338.76</v>
+        <v>58295.85</v>
       </c>
       <c r="D74" s="22">
-        <v>3302.15</v>
+        <v>223.45</v>
       </c>
       <c r="E74" s="24">
-        <v>0.099</v>
+        <v>0.0038</v>
       </c>
       <c r="F74" s="22">
-        <v>30036.61</v>
+        <v>58072.4</v>
       </c>
       <c r="G74" s="24">
-        <v>0.901</v>
+        <v>0.9962</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="17.45">
@@ -3852,23 +3852,23 @@
       </c>
       <c r="B75" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C75" s="22">
-        <v>38881.49</v>
+        <v>26119.93</v>
       </c>
       <c r="D75" s="22">
-        <v>0.0</v>
+        <v>10595.37</v>
       </c>
       <c r="E75" s="24">
-        <v>0.0</v>
+        <v>0.4056</v>
       </c>
       <c r="F75" s="22">
-        <v>38881.49</v>
+        <v>15524.56</v>
       </c>
       <c r="G75" s="24">
-        <v>1.0</v>
+        <v>0.5944</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="17.45">
@@ -3879,23 +3879,23 @@
       </c>
       <c r="B76" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C76" s="22">
-        <v>11600.08</v>
+        <v>33338.76</v>
       </c>
       <c r="D76" s="22">
-        <v>2017.31</v>
+        <v>3302.15</v>
       </c>
       <c r="E76" s="24">
-        <v>0.1739</v>
+        <v>0.099</v>
       </c>
       <c r="F76" s="22">
-        <v>9582.77</v>
+        <v>30036.61</v>
       </c>
       <c r="G76" s="24">
-        <v>0.8261</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="17.45">
@@ -3933,50 +3933,50 @@
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C78" s="22">
-        <v>2874.21</v>
+        <v>38881.49</v>
       </c>
       <c r="D78" s="22">
-        <v>2874.21</v>
+        <v>0.0</v>
       </c>
       <c r="E78" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F78" s="22">
-        <v>0.0</v>
+        <v>38881.49</v>
       </c>
       <c r="G78" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="17.45">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>Electrical Sheets (other than GOES) - 3.B</t>
+          <t>Metallic Coated Sheets - 4.A</t>
         </is>
       </c>
       <c r="B79" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C79" s="22">
-        <v>554.14</v>
+        <v>11600.08</v>
       </c>
       <c r="D79" s="22">
-        <v>0.0</v>
+        <v>2017.31</v>
       </c>
       <c r="E79" s="24">
-        <v>0.0</v>
+        <v>0.1739</v>
       </c>
       <c r="F79" s="22">
-        <v>554.14</v>
+        <v>9582.77</v>
       </c>
       <c r="G79" s="24">
-        <v>1.0</v>
+        <v>0.8261</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="17.45">
@@ -3987,23 +3987,23 @@
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C80" s="22">
-        <v>2943.83</v>
+        <v>2874.21</v>
       </c>
       <c r="D80" s="22">
-        <v>9.48</v>
+        <v>2874.21</v>
       </c>
       <c r="E80" s="24">
-        <v>0.0032</v>
+        <v>1.0</v>
       </c>
       <c r="F80" s="22">
-        <v>2934.35</v>
+        <v>0.0</v>
       </c>
       <c r="G80" s="24">
-        <v>0.9968</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="17.45">
@@ -4014,50 +4014,50 @@
       </c>
       <c r="B81" s="21" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C81" s="22">
-        <v>3150.34</v>
+        <v>2943.83</v>
       </c>
       <c r="D81" s="22">
-        <v>0.0</v>
+        <v>9.48</v>
       </c>
       <c r="E81" s="24">
-        <v>0.0</v>
+        <v>0.0032</v>
       </c>
       <c r="F81" s="22">
-        <v>3150.34</v>
+        <v>2934.35</v>
       </c>
       <c r="G81" s="24">
-        <v>1.0</v>
+        <v>0.9968</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="17.45">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>Metallic Coated Sheets - 4.B</t>
+          <t>Metallic Coated Sheets - 4.A</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C82" s="22">
-        <v>110698.86</v>
+        <v>3150.34</v>
       </c>
       <c r="D82" s="22">
-        <v>38591.47</v>
+        <v>0.0</v>
       </c>
       <c r="E82" s="24">
-        <v>0.3486</v>
+        <v>0.0</v>
       </c>
       <c r="F82" s="22">
-        <v>72107.39</v>
+        <v>3150.34</v>
       </c>
       <c r="G82" s="24">
-        <v>0.6514</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="17.45">
@@ -4068,23 +4068,23 @@
       </c>
       <c r="B83" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C83" s="22">
-        <v>45749.21</v>
+        <v>110698.86</v>
       </c>
       <c r="D83" s="22">
-        <v>45749.21</v>
+        <v>38591.47</v>
       </c>
       <c r="E83" s="24">
-        <v>1.0</v>
+        <v>0.3486</v>
       </c>
       <c r="F83" s="22">
-        <v>0.0</v>
+        <v>72107.39</v>
       </c>
       <c r="G83" s="24">
-        <v>0.0</v>
+        <v>0.6514</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="17.45">
@@ -4095,23 +4095,23 @@
       </c>
       <c r="B84" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C84" s="22">
-        <v>34302.33</v>
+        <v>45749.21</v>
       </c>
       <c r="D84" s="22">
-        <v>148.63</v>
+        <v>45749.21</v>
       </c>
       <c r="E84" s="24">
-        <v>0.0043</v>
+        <v>1.0</v>
       </c>
       <c r="F84" s="22">
-        <v>34153.7</v>
+        <v>0.0</v>
       </c>
       <c r="G84" s="24">
-        <v>0.9957</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="17.45">
@@ -4122,23 +4122,23 @@
       </c>
       <c r="B85" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C85" s="22">
-        <v>26019.96</v>
+        <v>34302.33</v>
       </c>
       <c r="D85" s="22">
-        <v>26019.96</v>
+        <v>148.63</v>
       </c>
       <c r="E85" s="24">
-        <v>1.0</v>
+        <v>0.0043</v>
       </c>
       <c r="F85" s="22">
-        <v>0.0</v>
+        <v>34153.7</v>
       </c>
       <c r="G85" s="24">
-        <v>0.0</v>
+        <v>0.9957</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="17.45">
@@ -4149,14 +4149,14 @@
       </c>
       <c r="B86" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C86" s="22">
-        <v>23174.68</v>
+        <v>26019.96</v>
       </c>
       <c r="D86" s="22">
-        <v>23174.68</v>
+        <v>26019.96</v>
       </c>
       <c r="E86" s="24">
         <v>1.0</v>
@@ -4176,23 +4176,23 @@
       </c>
       <c r="B87" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C87" s="22">
-        <v>19514.4</v>
+        <v>25510.91</v>
       </c>
       <c r="D87" s="22">
-        <v>0.0</v>
+        <v>280.06</v>
       </c>
       <c r="E87" s="24">
-        <v>0.0</v>
+        <v>0.011</v>
       </c>
       <c r="F87" s="22">
-        <v>19514.4</v>
+        <v>25230.85</v>
       </c>
       <c r="G87" s="24">
-        <v>1.0</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="17.45">
@@ -4203,23 +4203,23 @@
       </c>
       <c r="B88" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C88" s="22">
-        <v>25510.91</v>
+        <v>19514.4</v>
       </c>
       <c r="D88" s="22">
-        <v>280.06</v>
+        <v>0.0</v>
       </c>
       <c r="E88" s="24">
-        <v>0.011</v>
+        <v>0.0</v>
       </c>
       <c r="F88" s="22">
-        <v>25230.85</v>
+        <v>19514.4</v>
       </c>
       <c r="G88" s="24">
-        <v>0.989</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="17.45">
@@ -4257,23 +4257,23 @@
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C90" s="22">
-        <v>314.48</v>
+        <v>23174.68</v>
       </c>
       <c r="D90" s="22">
-        <v>22.69</v>
+        <v>23174.68</v>
       </c>
       <c r="E90" s="24">
-        <v>0.0722</v>
+        <v>1.0</v>
       </c>
       <c r="F90" s="22">
-        <v>291.79</v>
+        <v>0.0</v>
       </c>
       <c r="G90" s="24">
-        <v>0.9278</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="17.45">
@@ -4284,50 +4284,50 @@
       </c>
       <c r="B91" s="21" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C91" s="22">
-        <v>1878.7</v>
+        <v>314.48</v>
       </c>
       <c r="D91" s="22">
-        <v>0.0</v>
+        <v>22.69</v>
       </c>
       <c r="E91" s="24">
-        <v>0.0</v>
+        <v>0.0722</v>
       </c>
       <c r="F91" s="22">
-        <v>1878.7</v>
+        <v>291.79</v>
       </c>
       <c r="G91" s="24">
-        <v>1.0</v>
+        <v>0.9278</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="17.45">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>Organic Coated Sheets - 5</t>
+          <t>Metallic Coated Sheets - 4.B</t>
         </is>
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C92" s="22">
-        <v>54334.43</v>
+        <v>1878.7</v>
       </c>
       <c r="D92" s="22">
-        <v>40035.71</v>
+        <v>0.0</v>
       </c>
       <c r="E92" s="24">
-        <v>0.7368</v>
+        <v>0.0</v>
       </c>
       <c r="F92" s="22">
-        <v>14298.72</v>
+        <v>1878.7</v>
       </c>
       <c r="G92" s="24">
-        <v>0.2632</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="17.45">
@@ -4338,23 +4338,23 @@
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C93" s="22">
-        <v>41828.13</v>
+        <v>54334.43</v>
       </c>
       <c r="D93" s="22">
-        <v>41828.13</v>
+        <v>40035.71</v>
       </c>
       <c r="E93" s="24">
-        <v>1.0</v>
+        <v>0.7368</v>
       </c>
       <c r="F93" s="22">
-        <v>0.0</v>
+        <v>14298.72</v>
       </c>
       <c r="G93" s="24">
-        <v>0.0</v>
+        <v>0.2632</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="17.45">
@@ -4365,23 +4365,23 @@
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C94" s="22">
-        <v>12605.9</v>
+        <v>41828.13</v>
       </c>
       <c r="D94" s="22">
-        <v>7101.45</v>
+        <v>41828.13</v>
       </c>
       <c r="E94" s="24">
-        <v>0.5633</v>
+        <v>1.0</v>
       </c>
       <c r="F94" s="22">
-        <v>5504.45</v>
+        <v>0.0</v>
       </c>
       <c r="G94" s="24">
-        <v>0.4367</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="17.45">
@@ -4419,23 +4419,23 @@
       </c>
       <c r="B96" s="21" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C96" s="22">
-        <v>5322.29</v>
+        <v>12605.9</v>
       </c>
       <c r="D96" s="22">
-        <v>3559.52</v>
+        <v>7101.45</v>
       </c>
       <c r="E96" s="24">
-        <v>0.6688</v>
+        <v>0.5633</v>
       </c>
       <c r="F96" s="22">
-        <v>1762.76</v>
+        <v>5504.45</v>
       </c>
       <c r="G96" s="24">
-        <v>0.3312</v>
+        <v>0.4367</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="17.45">
@@ -4473,23 +4473,23 @@
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C98" s="22">
-        <v>12575.71</v>
+        <v>5322.29</v>
       </c>
       <c r="D98" s="22">
-        <v>0.0</v>
+        <v>3559.52</v>
       </c>
       <c r="E98" s="24">
-        <v>0.0</v>
+        <v>0.6688</v>
       </c>
       <c r="F98" s="22">
-        <v>12575.71</v>
+        <v>1762.76</v>
       </c>
       <c r="G98" s="24">
-        <v>1.0</v>
+        <v>0.3312</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="17.45">
@@ -4500,23 +4500,23 @@
       </c>
       <c r="B99" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C99" s="22">
-        <v>1937.67</v>
+        <v>12575.71</v>
       </c>
       <c r="D99" s="22">
-        <v>73.41</v>
+        <v>0.0</v>
       </c>
       <c r="E99" s="24">
-        <v>0.0379</v>
+        <v>0.0</v>
       </c>
       <c r="F99" s="22">
-        <v>1864.26</v>
+        <v>12575.71</v>
       </c>
       <c r="G99" s="24">
-        <v>0.9621</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="17.45">
@@ -4527,23 +4527,23 @@
       </c>
       <c r="B100" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C100" s="22">
-        <v>6968.09</v>
+        <v>1937.67</v>
       </c>
       <c r="D100" s="22">
-        <v>214.19</v>
+        <v>73.41</v>
       </c>
       <c r="E100" s="24">
-        <v>0.0307</v>
+        <v>0.0379</v>
       </c>
       <c r="F100" s="22">
-        <v>6753.9</v>
+        <v>1864.26</v>
       </c>
       <c r="G100" s="24">
-        <v>0.9693</v>
+        <v>0.9621</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="17.45">
@@ -4554,50 +4554,50 @@
       </c>
       <c r="B101" s="21" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C101" s="22">
-        <v>1831.54</v>
+        <v>6968.09</v>
       </c>
       <c r="D101" s="22">
-        <v>99.82</v>
+        <v>214.19</v>
       </c>
       <c r="E101" s="24">
-        <v>0.0545</v>
+        <v>0.0307</v>
       </c>
       <c r="F101" s="22">
-        <v>1731.72</v>
+        <v>6753.9</v>
       </c>
       <c r="G101" s="24">
-        <v>0.9455</v>
+        <v>0.9693</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="17.45">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>Tin Mill products - 6</t>
+          <t>Organic Coated Sheets - 5</t>
         </is>
       </c>
       <c r="B102" s="21" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C102" s="22">
-        <v>15211.06</v>
+        <v>1831.54</v>
       </c>
       <c r="D102" s="22">
-        <v>434.98</v>
+        <v>99.82</v>
       </c>
       <c r="E102" s="24">
-        <v>0.0286</v>
+        <v>0.0545</v>
       </c>
       <c r="F102" s="22">
-        <v>14776.08</v>
+        <v>1731.72</v>
       </c>
       <c r="G102" s="24">
-        <v>0.9714</v>
+        <v>0.9455</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="17.45">
@@ -4662,23 +4662,23 @@
       </c>
       <c r="B105" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C105" s="22">
-        <v>14278.53</v>
+        <v>15211.06</v>
       </c>
       <c r="D105" s="22">
-        <v>2441.76</v>
+        <v>434.98</v>
       </c>
       <c r="E105" s="24">
-        <v>0.171</v>
+        <v>0.0286</v>
       </c>
       <c r="F105" s="22">
-        <v>11836.77</v>
+        <v>14776.08</v>
       </c>
       <c r="G105" s="24">
-        <v>0.829</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="17.45">
@@ -4689,23 +4689,23 @@
       </c>
       <c r="B106" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C106" s="22">
-        <v>13880.42</v>
+        <v>14278.53</v>
       </c>
       <c r="D106" s="22">
-        <v>4963.14</v>
+        <v>2441.76</v>
       </c>
       <c r="E106" s="24">
-        <v>0.3576</v>
+        <v>0.171</v>
       </c>
       <c r="F106" s="22">
-        <v>8917.28</v>
+        <v>11836.77</v>
       </c>
       <c r="G106" s="24">
-        <v>0.6424</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="17.45">
@@ -4716,23 +4716,23 @@
       </c>
       <c r="B107" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C107" s="22">
-        <v>6446.51</v>
+        <v>13880.42</v>
       </c>
       <c r="D107" s="22">
-        <v>3217.76</v>
+        <v>4963.14</v>
       </c>
       <c r="E107" s="24">
-        <v>0.4991</v>
+        <v>0.3576</v>
       </c>
       <c r="F107" s="22">
-        <v>3228.75</v>
+        <v>8917.28</v>
       </c>
       <c r="G107" s="24">
-        <v>0.5009</v>
+        <v>0.6424</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="17.45">
@@ -4770,11 +4770,11 @@
       </c>
       <c r="B109" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C109" s="22">
-        <v>11254.86</v>
+        <v>5977.74</v>
       </c>
       <c r="D109" s="22">
         <v>0.0</v>
@@ -4783,7 +4783,7 @@
         <v>0.0</v>
       </c>
       <c r="F109" s="22">
-        <v>11254.86</v>
+        <v>5977.74</v>
       </c>
       <c r="G109" s="24">
         <v>1.0</v>
@@ -4797,11 +4797,11 @@
       </c>
       <c r="B110" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C110" s="22">
-        <v>5977.74</v>
+        <v>11254.86</v>
       </c>
       <c r="D110" s="22">
         <v>0.0</v>
@@ -4810,7 +4810,7 @@
         <v>0.0</v>
       </c>
       <c r="F110" s="22">
-        <v>5977.74</v>
+        <v>11254.86</v>
       </c>
       <c r="G110" s="24">
         <v>1.0</v>
@@ -4824,23 +4824,23 @@
       </c>
       <c r="B111" s="21" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C111" s="22">
-        <v>20.53</v>
+        <v>2917.88</v>
       </c>
       <c r="D111" s="22">
-        <v>0.0</v>
+        <v>2917.88</v>
       </c>
       <c r="E111" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F111" s="22">
-        <v>20.53</v>
+        <v>0.0</v>
       </c>
       <c r="G111" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="17.45">
@@ -4851,23 +4851,23 @@
       </c>
       <c r="B112" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C112" s="22">
-        <v>2917.88</v>
+        <v>20.53</v>
       </c>
       <c r="D112" s="22">
-        <v>2917.88</v>
+        <v>0.0</v>
       </c>
       <c r="E112" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F112" s="22">
-        <v>0.0</v>
+        <v>20.53</v>
       </c>
       <c r="G112" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="17.45">
@@ -4905,23 +4905,23 @@
       </c>
       <c r="B114" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C114" s="22">
-        <v>23294.11</v>
+        <v>53152.58</v>
       </c>
       <c r="D114" s="22">
-        <v>0.0</v>
+        <v>6223.67</v>
       </c>
       <c r="E114" s="24">
-        <v>0.0</v>
+        <v>0.1171</v>
       </c>
       <c r="F114" s="22">
-        <v>23294.11</v>
+        <v>46928.91</v>
       </c>
       <c r="G114" s="24">
-        <v>1.0</v>
+        <v>0.8829</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="17.45">
@@ -4932,23 +4932,23 @@
       </c>
       <c r="B115" s="21" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C115" s="22">
-        <v>53152.58</v>
+        <v>52709.57</v>
       </c>
       <c r="D115" s="22">
-        <v>6223.67</v>
+        <v>3.14</v>
       </c>
       <c r="E115" s="24">
-        <v>0.1171</v>
+        <v>0.0001</v>
       </c>
       <c r="F115" s="22">
-        <v>46928.91</v>
+        <v>52706.43</v>
       </c>
       <c r="G115" s="24">
-        <v>0.8829</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="17.45">
@@ -4959,23 +4959,23 @@
       </c>
       <c r="B116" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C116" s="22">
-        <v>52709.57</v>
+        <v>23294.11</v>
       </c>
       <c r="D116" s="22">
-        <v>3.14</v>
+        <v>0.0</v>
       </c>
       <c r="E116" s="24">
-        <v>0.0001</v>
+        <v>0.0</v>
       </c>
       <c r="F116" s="22">
-        <v>52706.43</v>
+        <v>23294.11</v>
       </c>
       <c r="G116" s="24">
-        <v>0.9999</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="17.45">
@@ -4986,23 +4986,23 @@
       </c>
       <c r="B117" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C117" s="22">
-        <v>8284.85</v>
+        <v>20671.86</v>
       </c>
       <c r="D117" s="22">
-        <v>639.61</v>
+        <v>1456.47</v>
       </c>
       <c r="E117" s="24">
-        <v>0.0772</v>
+        <v>0.0705</v>
       </c>
       <c r="F117" s="22">
-        <v>7645.24</v>
+        <v>19215.39</v>
       </c>
       <c r="G117" s="24">
-        <v>0.9228</v>
+        <v>0.9295</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="17.45">
@@ -5013,23 +5013,23 @@
       </c>
       <c r="B118" s="21" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C118" s="22">
-        <v>20671.86</v>
+        <v>8284.85</v>
       </c>
       <c r="D118" s="22">
-        <v>1456.47</v>
+        <v>639.61</v>
       </c>
       <c r="E118" s="24">
-        <v>0.0705</v>
+        <v>0.0772</v>
       </c>
       <c r="F118" s="22">
-        <v>19215.39</v>
+        <v>7645.24</v>
       </c>
       <c r="G118" s="24">
-        <v>0.9295</v>
+        <v>0.9228</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="17.45">
@@ -5143,28 +5143,28 @@
     <row r="123" spans="1:7" ht="17.45">
       <c r="A123" s="21" t="inlineStr">
         <is>
-          <t>Non Alloy and Other Alloy Quarto Plates - 7</t>
+          <t>Tin Mill products - 6</t>
         </is>
       </c>
       <c r="B123" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C123" s="22">
-        <v>5260.44</v>
+        <v>6446.51</v>
       </c>
       <c r="D123" s="22">
-        <v>0.0</v>
+        <v>3217.76</v>
       </c>
       <c r="E123" s="24">
-        <v>0.0</v>
+        <v>0.4991</v>
       </c>
       <c r="F123" s="22">
-        <v>5260.44</v>
+        <v>3228.75</v>
       </c>
       <c r="G123" s="24">
-        <v>1.0</v>
+        <v>0.5009</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="17.45">
@@ -5197,16 +5197,16 @@
     <row r="125" spans="1:7" ht="17.45">
       <c r="A125" s="21" t="inlineStr">
         <is>
-          <t>Stainless Hot Rolled Sheets and Strips - 8</t>
+          <t>Non Alloy and Other Alloy Quarto Plates - 7</t>
         </is>
       </c>
       <c r="B125" s="21" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
         </is>
       </c>
       <c r="C125" s="22">
-        <v>8960.7</v>
+        <v>5260.44</v>
       </c>
       <c r="D125" s="22">
         <v>0.0</v>
@@ -5215,7 +5215,7 @@
         <v>0.0</v>
       </c>
       <c r="F125" s="22">
-        <v>8960.7</v>
+        <v>5260.44</v>
       </c>
       <c r="G125" s="24">
         <v>1.0</v>
@@ -5229,23 +5229,23 @@
       </c>
       <c r="B126" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C126" s="22">
-        <v>3431.79</v>
+        <v>8960.7</v>
       </c>
       <c r="D126" s="22">
-        <v>1.05</v>
+        <v>0.0</v>
       </c>
       <c r="E126" s="24">
-        <v>0.0003</v>
+        <v>0.0</v>
       </c>
       <c r="F126" s="22">
-        <v>3430.74</v>
+        <v>8960.7</v>
       </c>
       <c r="G126" s="24">
-        <v>0.9997</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="17.45">
@@ -5337,23 +5337,23 @@
       </c>
       <c r="B130" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C130" s="22">
-        <v>2806.15</v>
+        <v>3021.64</v>
       </c>
       <c r="D130" s="22">
-        <v>0.0</v>
+        <v>296.37</v>
       </c>
       <c r="E130" s="24">
-        <v>0.0</v>
+        <v>0.0981</v>
       </c>
       <c r="F130" s="22">
-        <v>2806.15</v>
+        <v>2725.27</v>
       </c>
       <c r="G130" s="24">
-        <v>1.0</v>
+        <v>0.9019</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="17.45">
@@ -5364,50 +5364,50 @@
       </c>
       <c r="B131" s="21" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C131" s="22">
-        <v>3021.64</v>
+        <v>3431.79</v>
       </c>
       <c r="D131" s="22">
-        <v>296.37</v>
+        <v>1.05</v>
       </c>
       <c r="E131" s="24">
-        <v>0.0981</v>
+        <v>0.0003</v>
       </c>
       <c r="F131" s="22">
-        <v>2725.27</v>
+        <v>3430.74</v>
       </c>
       <c r="G131" s="24">
-        <v>0.9019</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="17.45">
       <c r="A132" s="21" t="inlineStr">
         <is>
-          <t>Stainless Cold Rolled Sheets and Strips - 9</t>
+          <t>Stainless Hot Rolled Sheets and Strips - 8</t>
         </is>
       </c>
       <c r="B132" s="21" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C132" s="22">
-        <v>13246.22</v>
+        <v>572.32</v>
       </c>
       <c r="D132" s="22">
-        <v>16.35</v>
+        <v>16.05</v>
       </c>
       <c r="E132" s="24">
-        <v>0.0012</v>
+        <v>0.028</v>
       </c>
       <c r="F132" s="22">
-        <v>13229.87</v>
+        <v>556.27</v>
       </c>
       <c r="G132" s="24">
-        <v>0.9988</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="17.45">
@@ -5418,23 +5418,23 @@
       </c>
       <c r="B133" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C133" s="22">
-        <v>572.32</v>
+        <v>2806.15</v>
       </c>
       <c r="D133" s="22">
-        <v>16.05</v>
+        <v>0.0</v>
       </c>
       <c r="E133" s="24">
-        <v>0.028</v>
+        <v>0.0</v>
       </c>
       <c r="F133" s="22">
-        <v>556.27</v>
+        <v>2806.15</v>
       </c>
       <c r="G133" s="24">
-        <v>0.972</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="17.45">
@@ -5499,23 +5499,23 @@
       </c>
       <c r="B136" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C136" s="22">
-        <v>10107.74</v>
+        <v>25471.04</v>
       </c>
       <c r="D136" s="22">
-        <v>302.68</v>
+        <v>675.22</v>
       </c>
       <c r="E136" s="24">
-        <v>0.0299</v>
+        <v>0.0265</v>
       </c>
       <c r="F136" s="22">
-        <v>9805.06</v>
+        <v>24795.82</v>
       </c>
       <c r="G136" s="24">
-        <v>0.9701</v>
+        <v>0.9735</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="17.45">
@@ -5526,23 +5526,23 @@
       </c>
       <c r="B137" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C137" s="22">
-        <v>25471.04</v>
+        <v>13246.22</v>
       </c>
       <c r="D137" s="22">
-        <v>675.22</v>
+        <v>16.35</v>
       </c>
       <c r="E137" s="24">
-        <v>0.0265</v>
+        <v>0.0012</v>
       </c>
       <c r="F137" s="22">
-        <v>24795.82</v>
+        <v>13229.87</v>
       </c>
       <c r="G137" s="24">
-        <v>0.9735</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="17.45">
@@ -5553,23 +5553,23 @@
       </c>
       <c r="B138" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C138" s="22">
-        <v>17259.54</v>
+        <v>10107.74</v>
       </c>
       <c r="D138" s="22">
-        <v>1829.65</v>
+        <v>302.68</v>
       </c>
       <c r="E138" s="24">
-        <v>0.106</v>
+        <v>0.0299</v>
       </c>
       <c r="F138" s="22">
-        <v>15429.89</v>
+        <v>9805.06</v>
       </c>
       <c r="G138" s="24">
-        <v>0.894</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="17.45">
@@ -5580,23 +5580,23 @@
       </c>
       <c r="B139" s="21" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C139" s="22">
-        <v>10963.33</v>
+        <v>17259.54</v>
       </c>
       <c r="D139" s="22">
-        <v>23.56</v>
+        <v>1829.65</v>
       </c>
       <c r="E139" s="24">
-        <v>0.0021</v>
+        <v>0.106</v>
       </c>
       <c r="F139" s="22">
-        <v>10939.77</v>
+        <v>15429.89</v>
       </c>
       <c r="G139" s="24">
-        <v>0.9979</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="17.45">
@@ -5634,23 +5634,23 @@
       </c>
       <c r="B141" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C141" s="22">
-        <v>9935.34</v>
+        <v>9513.44</v>
       </c>
       <c r="D141" s="22">
-        <v>0.0</v>
+        <v>340.87</v>
       </c>
       <c r="E141" s="24">
-        <v>0.0</v>
+        <v>0.0358</v>
       </c>
       <c r="F141" s="22">
-        <v>9935.34</v>
+        <v>9172.57</v>
       </c>
       <c r="G141" s="24">
-        <v>1.0</v>
+        <v>0.9642</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="17.45">
@@ -5661,23 +5661,23 @@
       </c>
       <c r="B142" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C142" s="22">
-        <v>9513.44</v>
+        <v>9935.34</v>
       </c>
       <c r="D142" s="22">
-        <v>340.87</v>
+        <v>0.0</v>
       </c>
       <c r="E142" s="24">
-        <v>0.0358</v>
+        <v>0.0</v>
       </c>
       <c r="F142" s="22">
-        <v>9172.57</v>
+        <v>9935.34</v>
       </c>
       <c r="G142" s="24">
-        <v>0.9642</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="17.45">
@@ -5688,23 +5688,23 @@
       </c>
       <c r="B143" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C143" s="22">
-        <v>8442.57</v>
+        <v>10963.33</v>
       </c>
       <c r="D143" s="22">
-        <v>592.14</v>
+        <v>23.56</v>
       </c>
       <c r="E143" s="24">
-        <v>0.0701</v>
+        <v>0.0021</v>
       </c>
       <c r="F143" s="22">
-        <v>7850.43</v>
+        <v>10939.77</v>
       </c>
       <c r="G143" s="24">
-        <v>0.9299</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="17.45">
@@ -5742,23 +5742,23 @@
       </c>
       <c r="B145" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C145" s="22">
-        <v>31.27</v>
+        <v>8442.57</v>
       </c>
       <c r="D145" s="22">
-        <v>0.0</v>
+        <v>592.14</v>
       </c>
       <c r="E145" s="24">
-        <v>0.0</v>
+        <v>0.0701</v>
       </c>
       <c r="F145" s="22">
-        <v>31.27</v>
+        <v>7850.43</v>
       </c>
       <c r="G145" s="24">
-        <v>1.0</v>
+        <v>0.9299</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="17.45">
@@ -5791,28 +5791,28 @@
     <row r="147" spans="1:7" ht="17.45">
       <c r="A147" s="21" t="inlineStr">
         <is>
-          <t>Stainless Hot Rolled Quarto Plates - 10</t>
+          <t>Stainless Cold Rolled Sheets and Strips - 9</t>
         </is>
       </c>
       <c r="B147" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
         </is>
       </c>
       <c r="C147" s="22">
-        <v>928.49</v>
+        <v>31.27</v>
       </c>
       <c r="D147" s="22">
-        <v>7.99</v>
+        <v>0.0</v>
       </c>
       <c r="E147" s="24">
-        <v>0.0086</v>
+        <v>0.0</v>
       </c>
       <c r="F147" s="22">
-        <v>920.5</v>
+        <v>31.27</v>
       </c>
       <c r="G147" s="24">
-        <v>0.9914</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="17.45">
@@ -5823,23 +5823,23 @@
       </c>
       <c r="B148" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C148" s="22">
-        <v>1497.03</v>
+        <v>928.49</v>
       </c>
       <c r="D148" s="22">
-        <v>439.99</v>
+        <v>7.99</v>
       </c>
       <c r="E148" s="24">
-        <v>0.2939</v>
+        <v>0.0086</v>
       </c>
       <c r="F148" s="22">
-        <v>1057.04</v>
+        <v>920.5</v>
       </c>
       <c r="G148" s="24">
-        <v>0.7061</v>
+        <v>0.9914</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="17.45">
@@ -5850,23 +5850,23 @@
       </c>
       <c r="B149" s="21" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C149" s="22">
-        <v>494.45</v>
+        <v>1497.03</v>
       </c>
       <c r="D149" s="22">
-        <v>26.82</v>
+        <v>439.99</v>
       </c>
       <c r="E149" s="24">
-        <v>0.0542</v>
+        <v>0.2939</v>
       </c>
       <c r="F149" s="22">
-        <v>467.63</v>
+        <v>1057.04</v>
       </c>
       <c r="G149" s="24">
-        <v>0.9458</v>
+        <v>0.7061</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="17.45">
@@ -5904,23 +5904,23 @@
       </c>
       <c r="B151" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C151" s="22">
-        <v>278.54</v>
+        <v>271.38</v>
       </c>
       <c r="D151" s="22">
-        <v>0.0</v>
+        <v>22.7</v>
       </c>
       <c r="E151" s="24">
-        <v>0.0</v>
+        <v>0.0837</v>
       </c>
       <c r="F151" s="22">
-        <v>278.54</v>
+        <v>248.68</v>
       </c>
       <c r="G151" s="24">
-        <v>1.0</v>
+        <v>0.9163</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="17.45">
@@ -5931,23 +5931,23 @@
       </c>
       <c r="B152" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C152" s="22">
-        <v>271.38</v>
+        <v>494.45</v>
       </c>
       <c r="D152" s="22">
-        <v>22.7</v>
+        <v>26.82</v>
       </c>
       <c r="E152" s="24">
-        <v>0.0837</v>
+        <v>0.0542</v>
       </c>
       <c r="F152" s="22">
-        <v>248.68</v>
+        <v>467.63</v>
       </c>
       <c r="G152" s="24">
-        <v>0.9163</v>
+        <v>0.9458</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="17.45">
@@ -5958,11 +5958,11 @@
       </c>
       <c r="B153" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C153" s="22">
-        <v>271.23</v>
+        <v>278.54</v>
       </c>
       <c r="D153" s="22">
         <v>0.0</v>
@@ -5971,7 +5971,7 @@
         <v>0.0</v>
       </c>
       <c r="F153" s="22">
-        <v>271.23</v>
+        <v>278.54</v>
       </c>
       <c r="G153" s="24">
         <v>1.0</v>
@@ -5980,28 +5980,28 @@
     <row r="154" spans="1:7" ht="17.45">
       <c r="A154" s="21" t="inlineStr">
         <is>
-          <t>Non Alloy and Other Alloy Merchant Bars and Light Sections - 12</t>
+          <t>Stainless Hot Rolled Quarto Plates - 10</t>
         </is>
       </c>
       <c r="B154" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C154" s="22">
-        <v>39484.18</v>
+        <v>271.23</v>
       </c>
       <c r="D154" s="22">
-        <v>3628.52</v>
+        <v>0.0</v>
       </c>
       <c r="E154" s="24">
-        <v>0.0919</v>
+        <v>0.0</v>
       </c>
       <c r="F154" s="22">
-        <v>35855.66</v>
+        <v>271.23</v>
       </c>
       <c r="G154" s="24">
-        <v>0.9081</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="17.45">
@@ -6012,23 +6012,23 @@
       </c>
       <c r="B155" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C155" s="22">
-        <v>26097.89</v>
+        <v>39484.18</v>
       </c>
       <c r="D155" s="22">
-        <v>652.59</v>
+        <v>3628.52</v>
       </c>
       <c r="E155" s="24">
-        <v>0.025</v>
+        <v>0.0919</v>
       </c>
       <c r="F155" s="22">
-        <v>25445.3</v>
+        <v>35855.66</v>
       </c>
       <c r="G155" s="24">
-        <v>0.975</v>
+        <v>0.9081</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="17.45">
@@ -6066,23 +6066,23 @@
       </c>
       <c r="B157" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C157" s="22">
-        <v>24360.31</v>
+        <v>26097.89</v>
       </c>
       <c r="D157" s="22">
-        <v>1046.87</v>
+        <v>652.59</v>
       </c>
       <c r="E157" s="24">
-        <v>0.043</v>
+        <v>0.025</v>
       </c>
       <c r="F157" s="22">
-        <v>23313.44</v>
+        <v>25445.3</v>
       </c>
       <c r="G157" s="24">
-        <v>0.957</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="17.45">
@@ -6093,23 +6093,23 @@
       </c>
       <c r="B158" s="21" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C158" s="22">
-        <v>13617.58</v>
+        <v>24360.31</v>
       </c>
       <c r="D158" s="22">
-        <v>744.47</v>
+        <v>1046.87</v>
       </c>
       <c r="E158" s="24">
-        <v>0.0547</v>
+        <v>0.043</v>
       </c>
       <c r="F158" s="22">
-        <v>12873.11</v>
+        <v>23313.44</v>
       </c>
       <c r="G158" s="24">
-        <v>0.9453</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="17.45">
@@ -6174,23 +6174,23 @@
       </c>
       <c r="B161" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C161" s="22">
-        <v>11809.9</v>
+        <v>13617.58</v>
       </c>
       <c r="D161" s="22">
-        <v>3190.46</v>
+        <v>744.47</v>
       </c>
       <c r="E161" s="24">
-        <v>0.2702</v>
+        <v>0.0547</v>
       </c>
       <c r="F161" s="22">
-        <v>8619.44</v>
+        <v>12873.11</v>
       </c>
       <c r="G161" s="24">
-        <v>0.7298</v>
+        <v>0.9453</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="17.45">
@@ -6201,23 +6201,23 @@
       </c>
       <c r="B162" s="21" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C162" s="22">
-        <v>3046.26</v>
+        <v>10862.95</v>
       </c>
       <c r="D162" s="22">
-        <v>103.56</v>
+        <v>109.14</v>
       </c>
       <c r="E162" s="24">
-        <v>0.034</v>
+        <v>0.01</v>
       </c>
       <c r="F162" s="22">
-        <v>2942.7</v>
+        <v>10753.81</v>
       </c>
       <c r="G162" s="24">
-        <v>0.966</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="17.45">
@@ -6228,23 +6228,23 @@
       </c>
       <c r="B163" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C163" s="22">
-        <v>10862.95</v>
+        <v>11809.9</v>
       </c>
       <c r="D163" s="22">
-        <v>109.14</v>
+        <v>3190.46</v>
       </c>
       <c r="E163" s="24">
-        <v>0.01</v>
+        <v>0.2702</v>
       </c>
       <c r="F163" s="22">
-        <v>10753.81</v>
+        <v>8619.44</v>
       </c>
       <c r="G163" s="24">
-        <v>0.99</v>
+        <v>0.7298</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="17.45">
@@ -6304,28 +6304,28 @@
     <row r="166" spans="1:7" ht="17.45">
       <c r="A166" s="21" t="inlineStr">
         <is>
-          <t>Rebars - 13</t>
+          <t>Non Alloy and Other Alloy Merchant Bars and Light Sections - 12</t>
         </is>
       </c>
       <c r="B166" s="21" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C166" s="22">
-        <v>15940.36</v>
+        <v>3046.26</v>
       </c>
       <c r="D166" s="22">
-        <v>7460.72</v>
+        <v>103.56</v>
       </c>
       <c r="E166" s="24">
-        <v>0.468</v>
+        <v>0.034</v>
       </c>
       <c r="F166" s="22">
-        <v>8479.64</v>
+        <v>2942.7</v>
       </c>
       <c r="G166" s="24">
-        <v>0.532</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="17.45">
@@ -6336,23 +6336,23 @@
       </c>
       <c r="B167" s="21" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C167" s="22">
-        <v>36091.95</v>
+        <v>15940.36</v>
       </c>
       <c r="D167" s="22">
-        <v>11313.03</v>
+        <v>7460.72</v>
       </c>
       <c r="E167" s="24">
-        <v>0.3135</v>
+        <v>0.468</v>
       </c>
       <c r="F167" s="22">
-        <v>24778.92</v>
+        <v>8479.64</v>
       </c>
       <c r="G167" s="24">
-        <v>0.6865</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="17.45">
@@ -6363,23 +6363,23 @@
       </c>
       <c r="B168" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C168" s="22">
-        <v>5054.03</v>
+        <v>36091.95</v>
       </c>
       <c r="D168" s="22">
-        <v>81.22</v>
+        <v>11313.03</v>
       </c>
       <c r="E168" s="24">
-        <v>0.0161</v>
+        <v>0.3135</v>
       </c>
       <c r="F168" s="22">
-        <v>4972.81</v>
+        <v>24778.92</v>
       </c>
       <c r="G168" s="24">
-        <v>0.9839</v>
+        <v>0.6865</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="17.45">
@@ -6444,23 +6444,23 @@
       </c>
       <c r="B171" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C171" s="22">
-        <v>39700.84</v>
+        <v>15830.59</v>
       </c>
       <c r="D171" s="22">
-        <v>0.0</v>
+        <v>193.3</v>
       </c>
       <c r="E171" s="24">
-        <v>0.0</v>
+        <v>0.0122</v>
       </c>
       <c r="F171" s="22">
-        <v>39700.84</v>
+        <v>15637.3</v>
       </c>
       <c r="G171" s="24">
-        <v>1.0</v>
+        <v>0.9878</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="17.45">
@@ -6471,23 +6471,23 @@
       </c>
       <c r="B172" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C172" s="22">
-        <v>15830.59</v>
+        <v>39700.84</v>
       </c>
       <c r="D172" s="22">
-        <v>193.3</v>
+        <v>0.0</v>
       </c>
       <c r="E172" s="24">
-        <v>0.0122</v>
+        <v>0.0</v>
       </c>
       <c r="F172" s="22">
-        <v>15637.3</v>
+        <v>39700.84</v>
       </c>
       <c r="G172" s="24">
-        <v>0.9878</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="17.45">
@@ -6547,55 +6547,55 @@
     <row r="175" spans="1:7" ht="17.45">
       <c r="A175" s="21" t="inlineStr">
         <is>
-          <t>Stainless Bars and Light Sections - 14</t>
+          <t>Rebars - 13</t>
         </is>
       </c>
       <c r="B175" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
         </is>
       </c>
       <c r="C175" s="22">
-        <v>2696.52</v>
+        <v>2162.48</v>
       </c>
       <c r="D175" s="22">
-        <v>110.04</v>
+        <v>0.0</v>
       </c>
       <c r="E175" s="24">
-        <v>0.0408</v>
+        <v>0.0</v>
       </c>
       <c r="F175" s="22">
-        <v>2586.48</v>
+        <v>2162.48</v>
       </c>
       <c r="G175" s="24">
-        <v>0.9592</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="17.45">
       <c r="A176" s="21" t="inlineStr">
         <is>
-          <t>Rebars - 13</t>
+          <t>Stainless Bars and Light Sections - 14</t>
         </is>
       </c>
       <c r="B176" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C176" s="22">
-        <v>2162.48</v>
+        <v>2696.52</v>
       </c>
       <c r="D176" s="22">
-        <v>0.0</v>
+        <v>110.04</v>
       </c>
       <c r="E176" s="24">
-        <v>0.0</v>
+        <v>0.0408</v>
       </c>
       <c r="F176" s="22">
-        <v>2162.48</v>
+        <v>2586.48</v>
       </c>
       <c r="G176" s="24">
-        <v>1.0</v>
+        <v>0.9592</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="17.45">
@@ -6606,23 +6606,23 @@
       </c>
       <c r="B177" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C177" s="22">
-        <v>2029.23</v>
+        <v>896.35</v>
       </c>
       <c r="D177" s="22">
-        <v>124.25</v>
+        <v>284.79</v>
       </c>
       <c r="E177" s="24">
-        <v>0.0612</v>
+        <v>0.3177</v>
       </c>
       <c r="F177" s="22">
-        <v>1904.98</v>
+        <v>611.56</v>
       </c>
       <c r="G177" s="24">
-        <v>0.9388</v>
+        <v>0.6823</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="17.45">
@@ -6633,23 +6633,23 @@
       </c>
       <c r="B178" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C178" s="22">
-        <v>0.0</v>
+        <v>2029.23</v>
       </c>
       <c r="D178" s="22">
-        <v>0.0</v>
+        <v>124.25</v>
       </c>
       <c r="E178" s="24">
-        <v>0.0</v>
+        <v>0.0612</v>
       </c>
       <c r="F178" s="22">
-        <v>0.0</v>
+        <v>1904.98</v>
       </c>
       <c r="G178" s="24">
-        <v>0.0</v>
+        <v>0.9388</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="17.45">
@@ -6660,77 +6660,77 @@
       </c>
       <c r="B179" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C179" s="22">
-        <v>1530.08</v>
+        <v>2398.59</v>
       </c>
       <c r="D179" s="22">
-        <v>768.02</v>
+        <v>0.0</v>
       </c>
       <c r="E179" s="24">
-        <v>0.5019</v>
+        <v>0.0</v>
       </c>
       <c r="F179" s="22">
-        <v>762.06</v>
+        <v>2398.59</v>
       </c>
       <c r="G179" s="24">
-        <v>0.4981</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="17.45">
       <c r="A180" s="21" t="inlineStr">
         <is>
-          <t>Stainless Bars and Light Sections - 14</t>
+          <t>Rebars - 13</t>
         </is>
       </c>
       <c r="B180" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C180" s="22">
-        <v>2398.59</v>
+        <v>5054.03</v>
       </c>
       <c r="D180" s="22">
-        <v>0.0</v>
+        <v>81.22</v>
       </c>
       <c r="E180" s="24">
-        <v>0.0</v>
+        <v>0.0161</v>
       </c>
       <c r="F180" s="22">
-        <v>2398.59</v>
+        <v>4972.81</v>
       </c>
       <c r="G180" s="24">
-        <v>1.0</v>
+        <v>0.9839</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="17.45">
       <c r="A181" s="21" t="inlineStr">
         <is>
-          <t>Stainless Wire Rod - 15</t>
+          <t>Stainless Bars and Light Sections - 14</t>
         </is>
       </c>
       <c r="B181" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C181" s="22">
-        <v>4693.08</v>
+        <v>708.72</v>
       </c>
       <c r="D181" s="22">
-        <v>590.33</v>
+        <v>5.28</v>
       </c>
       <c r="E181" s="24">
-        <v>0.1258</v>
+        <v>0.0074</v>
       </c>
       <c r="F181" s="22">
-        <v>4102.75</v>
+        <v>703.44</v>
       </c>
       <c r="G181" s="24">
-        <v>0.8742</v>
+        <v>0.9926</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="17.45">
@@ -6741,23 +6741,23 @@
       </c>
       <c r="B182" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C182" s="22">
-        <v>708.72</v>
+        <v>1530.08</v>
       </c>
       <c r="D182" s="22">
-        <v>5.28</v>
+        <v>768.02</v>
       </c>
       <c r="E182" s="24">
-        <v>0.0074</v>
+        <v>0.5019</v>
       </c>
       <c r="F182" s="22">
-        <v>703.44</v>
+        <v>762.06</v>
       </c>
       <c r="G182" s="24">
-        <v>0.9926</v>
+        <v>0.4981</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="17.45">
@@ -6768,23 +6768,23 @@
       </c>
       <c r="B183" s="21" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C183" s="22">
-        <v>1076.23</v>
+        <v>4693.08</v>
       </c>
       <c r="D183" s="22">
-        <v>0.0</v>
+        <v>590.33</v>
       </c>
       <c r="E183" s="24">
-        <v>0.0</v>
+        <v>0.1258</v>
       </c>
       <c r="F183" s="22">
-        <v>1076.23</v>
+        <v>4102.75</v>
       </c>
       <c r="G183" s="24">
-        <v>1.0</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="17.45">
@@ -6822,23 +6822,23 @@
       </c>
       <c r="B185" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C185" s="22">
-        <v>998.52</v>
+        <v>1076.23</v>
       </c>
       <c r="D185" s="22">
-        <v>18.71</v>
+        <v>0.0</v>
       </c>
       <c r="E185" s="24">
-        <v>0.0187</v>
+        <v>0.0</v>
       </c>
       <c r="F185" s="22">
-        <v>979.81</v>
+        <v>1076.23</v>
       </c>
       <c r="G185" s="24">
-        <v>0.9813</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="17.45">
@@ -6849,23 +6849,23 @@
       </c>
       <c r="B186" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C186" s="22">
-        <v>343.53</v>
+        <v>998.52</v>
       </c>
       <c r="D186" s="22">
-        <v>0.0</v>
+        <v>18.71</v>
       </c>
       <c r="E186" s="24">
-        <v>0.0</v>
+        <v>0.0187</v>
       </c>
       <c r="F186" s="22">
-        <v>343.53</v>
+        <v>979.81</v>
       </c>
       <c r="G186" s="24">
-        <v>1.0</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="17.45">
@@ -6876,23 +6876,23 @@
       </c>
       <c r="B187" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C187" s="22">
-        <v>600.0</v>
+        <v>343.53</v>
       </c>
       <c r="D187" s="22">
-        <v>536.64</v>
+        <v>0.0</v>
       </c>
       <c r="E187" s="24">
-        <v>0.8944</v>
+        <v>0.0</v>
       </c>
       <c r="F187" s="22">
-        <v>63.36</v>
+        <v>343.53</v>
       </c>
       <c r="G187" s="24">
-        <v>0.1056</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="17.45">
@@ -6903,23 +6903,23 @@
       </c>
       <c r="B188" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C188" s="22">
-        <v>810.14</v>
+        <v>600.0</v>
       </c>
       <c r="D188" s="22">
-        <v>0.0</v>
+        <v>536.64</v>
       </c>
       <c r="E188" s="24">
-        <v>0.0</v>
+        <v>0.8944</v>
       </c>
       <c r="F188" s="22">
-        <v>810.14</v>
+        <v>63.36</v>
       </c>
       <c r="G188" s="24">
-        <v>1.0</v>
+        <v>0.1056</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="17.45">
@@ -6952,28 +6952,28 @@
     <row r="190" spans="1:7" ht="17.45">
       <c r="A190" s="21" t="inlineStr">
         <is>
-          <t>Non Alloy and Other Alloy Wire Rod - 16</t>
+          <t>Stainless Wire Rod - 15</t>
         </is>
       </c>
       <c r="B190" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C190" s="22">
-        <v>61147.25</v>
+        <v>145.69</v>
       </c>
       <c r="D190" s="22">
-        <v>61147.25</v>
+        <v>24.22</v>
       </c>
       <c r="E190" s="24">
-        <v>1.0</v>
+        <v>0.1663</v>
       </c>
       <c r="F190" s="22">
-        <v>0.0</v>
+        <v>121.47</v>
       </c>
       <c r="G190" s="24">
-        <v>0.0</v>
+        <v>0.8337</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="17.45">
@@ -6984,23 +6984,23 @@
       </c>
       <c r="B191" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C191" s="22">
-        <v>145.69</v>
+        <v>810.14</v>
       </c>
       <c r="D191" s="22">
-        <v>24.22</v>
+        <v>0.0</v>
       </c>
       <c r="E191" s="24">
-        <v>0.1663</v>
+        <v>0.0</v>
       </c>
       <c r="F191" s="22">
-        <v>121.47</v>
+        <v>810.14</v>
       </c>
       <c r="G191" s="24">
-        <v>0.8337</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="17.45">
@@ -7011,23 +7011,23 @@
       </c>
       <c r="B192" s="21" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C192" s="22">
-        <v>47286.26</v>
+        <v>61147.25</v>
       </c>
       <c r="D192" s="22">
-        <v>13848.24</v>
+        <v>61147.25</v>
       </c>
       <c r="E192" s="24">
-        <v>0.2929</v>
+        <v>1.0</v>
       </c>
       <c r="F192" s="22">
-        <v>33438.02</v>
+        <v>0.0</v>
       </c>
       <c r="G192" s="24">
-        <v>0.7071</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="17.45">
@@ -7092,23 +7092,23 @@
       </c>
       <c r="B195" s="21" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C195" s="22">
-        <v>23959.81</v>
+        <v>47286.26</v>
       </c>
       <c r="D195" s="22">
-        <v>0.0</v>
+        <v>13848.24</v>
       </c>
       <c r="E195" s="24">
-        <v>0.0</v>
+        <v>0.2929</v>
       </c>
       <c r="F195" s="22">
-        <v>23959.81</v>
+        <v>33438.02</v>
       </c>
       <c r="G195" s="24">
-        <v>1.0</v>
+        <v>0.7071</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="17.45">
@@ -7119,23 +7119,23 @@
       </c>
       <c r="B196" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C196" s="22">
-        <v>40548.83</v>
+        <v>24271.66</v>
       </c>
       <c r="D196" s="22">
-        <v>2593.38</v>
+        <v>8881.01</v>
       </c>
       <c r="E196" s="24">
-        <v>0.064</v>
+        <v>0.3659</v>
       </c>
       <c r="F196" s="22">
-        <v>37955.45</v>
+        <v>15390.65</v>
       </c>
       <c r="G196" s="24">
-        <v>0.936</v>
+        <v>0.6341</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="17.45">
@@ -7146,23 +7146,23 @@
       </c>
       <c r="B197" s="21" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C197" s="22">
-        <v>24271.66</v>
+        <v>40548.83</v>
       </c>
       <c r="D197" s="22">
-        <v>8881.01</v>
+        <v>2593.38</v>
       </c>
       <c r="E197" s="24">
-        <v>0.3659</v>
+        <v>0.064</v>
       </c>
       <c r="F197" s="22">
-        <v>15390.65</v>
+        <v>37955.45</v>
       </c>
       <c r="G197" s="24">
-        <v>0.6341</v>
+        <v>0.936</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="17.45">
@@ -7173,23 +7173,23 @@
       </c>
       <c r="B198" s="21" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C198" s="22">
-        <v>21678.72</v>
+        <v>23959.81</v>
       </c>
       <c r="D198" s="22">
-        <v>9419.05</v>
+        <v>0.0</v>
       </c>
       <c r="E198" s="24">
-        <v>0.4345</v>
+        <v>0.0</v>
       </c>
       <c r="F198" s="22">
-        <v>12259.67</v>
+        <v>23959.81</v>
       </c>
       <c r="G198" s="24">
-        <v>0.5655</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="17.45">
@@ -7200,23 +7200,23 @@
       </c>
       <c r="B199" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C199" s="22">
-        <v>30720.34</v>
+        <v>21678.72</v>
       </c>
       <c r="D199" s="22">
-        <v>0.0</v>
+        <v>9419.05</v>
       </c>
       <c r="E199" s="24">
-        <v>0.0</v>
+        <v>0.4345</v>
       </c>
       <c r="F199" s="22">
-        <v>30720.34</v>
+        <v>12259.67</v>
       </c>
       <c r="G199" s="24">
-        <v>1.0</v>
+        <v>0.5655</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="17.45">
@@ -7227,23 +7227,23 @@
       </c>
       <c r="B200" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C200" s="22">
-        <v>38481.84</v>
+        <v>30720.34</v>
       </c>
       <c r="D200" s="22">
-        <v>12.49</v>
+        <v>0.0</v>
       </c>
       <c r="E200" s="24">
-        <v>0.0003</v>
+        <v>0.0</v>
       </c>
       <c r="F200" s="22">
-        <v>38469.35</v>
+        <v>30720.34</v>
       </c>
       <c r="G200" s="24">
-        <v>0.9997</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="17.45">
@@ -7254,23 +7254,23 @@
       </c>
       <c r="B201" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C201" s="22">
-        <v>34610.24</v>
+        <v>38481.84</v>
       </c>
       <c r="D201" s="22">
-        <v>5181.09</v>
+        <v>12.49</v>
       </c>
       <c r="E201" s="24">
-        <v>0.1497</v>
+        <v>0.0003</v>
       </c>
       <c r="F201" s="22">
-        <v>29429.15</v>
+        <v>38469.35</v>
       </c>
       <c r="G201" s="24">
-        <v>0.8503</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="17.45">
@@ -7281,104 +7281,104 @@
       </c>
       <c r="B202" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C202" s="22">
-        <v>2833.69</v>
+        <v>34610.24</v>
       </c>
       <c r="D202" s="22">
-        <v>0.0</v>
+        <v>5181.09</v>
       </c>
       <c r="E202" s="24">
-        <v>0.0</v>
+        <v>0.1497</v>
       </c>
       <c r="F202" s="22">
-        <v>2833.69</v>
+        <v>29429.15</v>
       </c>
       <c r="G202" s="24">
-        <v>1.0</v>
+        <v>0.8503</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="17.45">
       <c r="A203" s="21" t="inlineStr">
         <is>
-          <t>Angles, Shapes and Sections of Iron or Non Alloy Steel - 17</t>
+          <t>Non Alloy and Other Alloy Wire Rod - 16</t>
         </is>
       </c>
       <c r="B203" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C203" s="22">
-        <v>5964.05</v>
+        <v>1323.5</v>
       </c>
       <c r="D203" s="22">
-        <v>133.0</v>
+        <v>258.48</v>
       </c>
       <c r="E203" s="24">
-        <v>0.0223</v>
+        <v>0.1953</v>
       </c>
       <c r="F203" s="22">
-        <v>5831.05</v>
+        <v>1065.03</v>
       </c>
       <c r="G203" s="24">
-        <v>0.9777</v>
+        <v>0.8047</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="17.45">
       <c r="A204" s="21" t="inlineStr">
         <is>
-          <t>Angles, Shapes and Sections of Iron or Non Alloy Steel - 17</t>
+          <t>Non Alloy and Other Alloy Wire Rod - 16</t>
         </is>
       </c>
       <c r="B204" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C204" s="22">
-        <v>13455.55</v>
+        <v>2833.69</v>
       </c>
       <c r="D204" s="22">
-        <v>9040.21</v>
+        <v>0.0</v>
       </c>
       <c r="E204" s="24">
-        <v>0.6719</v>
+        <v>0.0</v>
       </c>
       <c r="F204" s="22">
-        <v>4415.34</v>
+        <v>2833.69</v>
       </c>
       <c r="G204" s="24">
-        <v>0.3281</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="17.45">
       <c r="A205" s="21" t="inlineStr">
         <is>
-          <t>Non Alloy and Other Alloy Wire Rod - 16</t>
+          <t>Angles, Shapes and Sections of Iron or Non Alloy Steel - 17</t>
         </is>
       </c>
       <c r="B205" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C205" s="22">
-        <v>1323.5</v>
+        <v>13455.55</v>
       </c>
       <c r="D205" s="22">
-        <v>258.48</v>
+        <v>9040.21</v>
       </c>
       <c r="E205" s="24">
-        <v>0.1953</v>
+        <v>0.6719</v>
       </c>
       <c r="F205" s="22">
-        <v>1065.03</v>
+        <v>4415.34</v>
       </c>
       <c r="G205" s="24">
-        <v>0.8047</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="17.45">
@@ -7389,11 +7389,11 @@
       </c>
       <c r="B206" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C206" s="22">
-        <v>3032.46</v>
+        <v>2590.81</v>
       </c>
       <c r="D206" s="22">
         <v>0.0</v>
@@ -7402,7 +7402,7 @@
         <v>0.0</v>
       </c>
       <c r="F206" s="22">
-        <v>3032.46</v>
+        <v>2590.81</v>
       </c>
       <c r="G206" s="24">
         <v>1.0</v>
@@ -7416,23 +7416,23 @@
       </c>
       <c r="B207" s="21" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C207" s="22">
-        <v>1491.1</v>
+        <v>5964.05</v>
       </c>
       <c r="D207" s="22">
-        <v>0.0</v>
+        <v>133.0</v>
       </c>
       <c r="E207" s="24">
-        <v>0.0</v>
+        <v>0.0223</v>
       </c>
       <c r="F207" s="22">
-        <v>1491.1</v>
+        <v>5831.05</v>
       </c>
       <c r="G207" s="24">
-        <v>1.0</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="17.45">
@@ -7443,11 +7443,11 @@
       </c>
       <c r="B208" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C208" s="22">
-        <v>2590.81</v>
+        <v>3032.46</v>
       </c>
       <c r="D208" s="22">
         <v>0.0</v>
@@ -7456,7 +7456,7 @@
         <v>0.0</v>
       </c>
       <c r="F208" s="22">
-        <v>2590.81</v>
+        <v>3032.46</v>
       </c>
       <c r="G208" s="24">
         <v>1.0</v>
@@ -7470,23 +7470,23 @@
       </c>
       <c r="B209" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C209" s="22">
-        <v>3153.55</v>
+        <v>1491.1</v>
       </c>
       <c r="D209" s="22">
-        <v>509.92</v>
+        <v>0.0</v>
       </c>
       <c r="E209" s="24">
-        <v>0.1617</v>
+        <v>0.0</v>
       </c>
       <c r="F209" s="22">
-        <v>2643.63</v>
+        <v>1491.1</v>
       </c>
       <c r="G209" s="24">
-        <v>0.8383</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="17.45">
@@ -7497,23 +7497,23 @@
       </c>
       <c r="B210" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C210" s="22">
-        <v>1073.81</v>
+        <v>3153.55</v>
       </c>
       <c r="D210" s="22">
-        <v>0.0</v>
+        <v>509.92</v>
       </c>
       <c r="E210" s="24">
-        <v>0.0</v>
+        <v>0.1617</v>
       </c>
       <c r="F210" s="22">
-        <v>1073.81</v>
+        <v>2643.63</v>
       </c>
       <c r="G210" s="24">
-        <v>1.0</v>
+        <v>0.8383</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="17.45">
@@ -7546,82 +7546,82 @@
     <row r="212" spans="1:7" ht="17.45">
       <c r="A212" s="21" t="inlineStr">
         <is>
-          <t>Angles, Shapes and Sections of Iron or Non Alloy Steel - 17</t>
+          <t>Sheet Piling - 18</t>
         </is>
       </c>
       <c r="B212" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C212" s="22">
-        <v>14138.78</v>
+        <v>2480.61</v>
       </c>
       <c r="D212" s="22">
-        <v>0.0</v>
+        <v>2480.61</v>
       </c>
       <c r="E212" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F212" s="22">
-        <v>14138.78</v>
+        <v>0.0</v>
       </c>
       <c r="G212" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="17.45">
       <c r="A213" s="21" t="inlineStr">
         <is>
-          <t>Sheet Piling - 18</t>
+          <t>Angles, Shapes and Sections of Iron or Non Alloy Steel - 17</t>
         </is>
       </c>
       <c r="B213" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
         </is>
       </c>
       <c r="C213" s="22">
-        <v>2480.61</v>
+        <v>14138.78</v>
       </c>
       <c r="D213" s="22">
-        <v>2480.61</v>
+        <v>0.0</v>
       </c>
       <c r="E213" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F213" s="22">
-        <v>0.0</v>
+        <v>14138.78</v>
       </c>
       <c r="G213" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="17.45">
       <c r="A214" s="21" t="inlineStr">
         <is>
-          <t>Sheet Piling - 18</t>
+          <t>Angles, Shapes and Sections of Iron or Non Alloy Steel - 17</t>
         </is>
       </c>
       <c r="B214" s="21" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C214" s="22">
-        <v>903.08</v>
+        <v>1073.81</v>
       </c>
       <c r="D214" s="22">
-        <v>900.95</v>
+        <v>0.0</v>
       </c>
       <c r="E214" s="24">
-        <v>0.9976</v>
+        <v>0.0</v>
       </c>
       <c r="F214" s="22">
-        <v>2.13</v>
+        <v>1073.81</v>
       </c>
       <c r="G214" s="24">
-        <v>0.0024</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="17.45">
@@ -7632,23 +7632,23 @@
       </c>
       <c r="B215" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C215" s="22">
-        <v>1234.34</v>
+        <v>903.08</v>
       </c>
       <c r="D215" s="22">
-        <v>0.0</v>
+        <v>900.95</v>
       </c>
       <c r="E215" s="24">
-        <v>0.0</v>
+        <v>0.9976</v>
       </c>
       <c r="F215" s="22">
-        <v>1234.34</v>
+        <v>2.13</v>
       </c>
       <c r="G215" s="24">
-        <v>1.0</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="17.45">
@@ -7686,50 +7686,50 @@
       </c>
       <c r="B217" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C217" s="22">
-        <v>85.28</v>
+        <v>1234.34</v>
       </c>
       <c r="D217" s="22">
-        <v>16.02</v>
+        <v>0.0</v>
       </c>
       <c r="E217" s="24">
-        <v>0.1879</v>
+        <v>0.0</v>
       </c>
       <c r="F217" s="22">
-        <v>69.26</v>
+        <v>1234.34</v>
       </c>
       <c r="G217" s="24">
-        <v>0.8121</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="17.45">
       <c r="A218" s="21" t="inlineStr">
         <is>
-          <t>Railway Material - 19</t>
+          <t>Sheet Piling - 18</t>
         </is>
       </c>
       <c r="B218" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C218" s="22">
-        <v>1280.1</v>
+        <v>1445.52</v>
       </c>
       <c r="D218" s="22">
-        <v>263.69</v>
+        <v>1.58</v>
       </c>
       <c r="E218" s="24">
-        <v>0.206</v>
+        <v>0.0011</v>
       </c>
       <c r="F218" s="22">
-        <v>1016.41</v>
+        <v>1443.94</v>
       </c>
       <c r="G218" s="24">
-        <v>0.794</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="17.45">
@@ -7740,23 +7740,23 @@
       </c>
       <c r="B219" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C219" s="22">
-        <v>1445.52</v>
+        <v>85.28</v>
       </c>
       <c r="D219" s="22">
-        <v>1.58</v>
+        <v>16.02</v>
       </c>
       <c r="E219" s="24">
-        <v>0.0011</v>
+        <v>0.1879</v>
       </c>
       <c r="F219" s="22">
-        <v>1443.94</v>
+        <v>69.26</v>
       </c>
       <c r="G219" s="24">
-        <v>0.9989</v>
+        <v>0.8121</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="17.45">
@@ -7767,23 +7767,23 @@
       </c>
       <c r="B220" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C220" s="22">
-        <v>421.09</v>
+        <v>1758.07</v>
       </c>
       <c r="D220" s="22">
-        <v>2.92</v>
+        <v>1.91</v>
       </c>
       <c r="E220" s="24">
-        <v>0.0069</v>
+        <v>0.0011</v>
       </c>
       <c r="F220" s="22">
-        <v>418.16</v>
+        <v>1756.16</v>
       </c>
       <c r="G220" s="24">
-        <v>0.9931</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="17.45">
@@ -7794,23 +7794,23 @@
       </c>
       <c r="B221" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C221" s="22">
-        <v>1758.07</v>
+        <v>220.46</v>
       </c>
       <c r="D221" s="22">
-        <v>1.91</v>
+        <v>32.95</v>
       </c>
       <c r="E221" s="24">
-        <v>0.0011</v>
+        <v>0.1495</v>
       </c>
       <c r="F221" s="22">
-        <v>1756.16</v>
+        <v>187.51</v>
       </c>
       <c r="G221" s="24">
-        <v>0.9989</v>
+        <v>0.8505</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="17.45">
@@ -7821,23 +7821,23 @@
       </c>
       <c r="B222" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C222" s="22">
-        <v>220.46</v>
+        <v>286.0</v>
       </c>
       <c r="D222" s="22">
-        <v>32.95</v>
+        <v>0.0</v>
       </c>
       <c r="E222" s="24">
-        <v>0.1495</v>
+        <v>0.0</v>
       </c>
       <c r="F222" s="22">
-        <v>187.51</v>
+        <v>286.0</v>
       </c>
       <c r="G222" s="24">
-        <v>0.8505</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="17.45">
@@ -7848,23 +7848,23 @@
       </c>
       <c r="B223" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C223" s="22">
-        <v>286.0</v>
+        <v>421.09</v>
       </c>
       <c r="D223" s="22">
-        <v>0.0</v>
+        <v>2.92</v>
       </c>
       <c r="E223" s="24">
-        <v>0.0</v>
+        <v>0.0069</v>
       </c>
       <c r="F223" s="22">
-        <v>286.0</v>
+        <v>418.16</v>
       </c>
       <c r="G223" s="24">
-        <v>1.0</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="17.45">
@@ -7875,23 +7875,23 @@
       </c>
       <c r="B224" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C224" s="22">
-        <v>152.35</v>
+        <v>1280.1</v>
       </c>
       <c r="D224" s="22">
-        <v>0.0</v>
+        <v>263.69</v>
       </c>
       <c r="E224" s="24">
-        <v>0.0</v>
+        <v>0.206</v>
       </c>
       <c r="F224" s="22">
-        <v>152.35</v>
+        <v>1016.41</v>
       </c>
       <c r="G224" s="24">
-        <v>1.0</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="17.45">
@@ -7902,14 +7902,14 @@
       </c>
       <c r="B225" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C225" s="22">
-        <v>10036.89</v>
+        <v>28163.03</v>
       </c>
       <c r="D225" s="22">
-        <v>10036.89</v>
+        <v>28163.03</v>
       </c>
       <c r="E225" s="24">
         <v>1.0</v>
@@ -7929,50 +7929,50 @@
       </c>
       <c r="B226" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C226" s="22">
-        <v>28163.03</v>
+        <v>3636.32</v>
       </c>
       <c r="D226" s="22">
-        <v>28163.03</v>
+        <v>1133.63</v>
       </c>
       <c r="E226" s="24">
-        <v>1.0</v>
+        <v>0.3118</v>
       </c>
       <c r="F226" s="22">
-        <v>0.0</v>
+        <v>2502.69</v>
       </c>
       <c r="G226" s="24">
-        <v>0.0</v>
+        <v>0.6882</v>
       </c>
     </row>
     <row r="227" spans="1:7" ht="17.45">
       <c r="A227" s="21" t="inlineStr">
         <is>
-          <t>Gas Pipes - 20</t>
+          <t>Railway Material - 19</t>
         </is>
       </c>
       <c r="B227" s="21" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C227" s="22">
-        <v>2521.72</v>
+        <v>152.35</v>
       </c>
       <c r="D227" s="22">
-        <v>24.63</v>
+        <v>0.0</v>
       </c>
       <c r="E227" s="24">
-        <v>0.0098</v>
+        <v>0.0</v>
       </c>
       <c r="F227" s="22">
-        <v>2497.09</v>
+        <v>152.35</v>
       </c>
       <c r="G227" s="24">
-        <v>0.9902</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="228" spans="1:7" ht="17.45">
@@ -7983,23 +7983,23 @@
       </c>
       <c r="B228" s="21" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C228" s="22">
-        <v>3636.32</v>
+        <v>10036.89</v>
       </c>
       <c r="D228" s="22">
-        <v>1133.63</v>
+        <v>10036.89</v>
       </c>
       <c r="E228" s="24">
-        <v>0.3118</v>
+        <v>1.0</v>
       </c>
       <c r="F228" s="22">
-        <v>2502.69</v>
+        <v>0.0</v>
       </c>
       <c r="G228" s="24">
-        <v>0.6882</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="229" spans="1:7" ht="17.45">
@@ -8010,23 +8010,23 @@
       </c>
       <c r="B229" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C229" s="22">
-        <v>3264.36</v>
+        <v>2521.72</v>
       </c>
       <c r="D229" s="22">
-        <v>260.99</v>
+        <v>24.63</v>
       </c>
       <c r="E229" s="24">
-        <v>0.08</v>
+        <v>0.0098</v>
       </c>
       <c r="F229" s="22">
-        <v>3003.37</v>
+        <v>2497.09</v>
       </c>
       <c r="G229" s="24">
-        <v>0.92</v>
+        <v>0.9902</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="17.45">
@@ -8037,23 +8037,23 @@
       </c>
       <c r="B230" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C230" s="22">
-        <v>1731.37</v>
+        <v>3264.36</v>
       </c>
       <c r="D230" s="22">
-        <v>29.58</v>
+        <v>260.99</v>
       </c>
       <c r="E230" s="24">
-        <v>0.0171</v>
+        <v>0.08</v>
       </c>
       <c r="F230" s="22">
-        <v>1701.79</v>
+        <v>3003.37</v>
       </c>
       <c r="G230" s="24">
-        <v>0.9829</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="17.45">
@@ -8091,50 +8091,50 @@
       </c>
       <c r="B232" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C232" s="22">
-        <v>2339.12</v>
+        <v>1731.37</v>
       </c>
       <c r="D232" s="22">
-        <v>352.61</v>
+        <v>29.58</v>
       </c>
       <c r="E232" s="24">
-        <v>0.1507</v>
+        <v>0.0171</v>
       </c>
       <c r="F232" s="22">
-        <v>1986.51</v>
+        <v>1701.79</v>
       </c>
       <c r="G232" s="24">
-        <v>0.8493</v>
+        <v>0.9829</v>
       </c>
     </row>
     <row r="233" spans="1:7" ht="17.45">
       <c r="A233" s="21" t="inlineStr">
         <is>
-          <t>Hollow Sections - 21</t>
+          <t>Gas Pipes - 20</t>
         </is>
       </c>
       <c r="B233" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C233" s="22">
-        <v>59849.63</v>
+        <v>2339.12</v>
       </c>
       <c r="D233" s="22">
-        <v>59849.63</v>
+        <v>352.61</v>
       </c>
       <c r="E233" s="24">
-        <v>1.0</v>
+        <v>0.1507</v>
       </c>
       <c r="F233" s="22">
-        <v>0.0</v>
+        <v>1986.51</v>
       </c>
       <c r="G233" s="24">
-        <v>0.0</v>
+        <v>0.8493</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="17.45">
@@ -8145,23 +8145,23 @@
       </c>
       <c r="B234" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C234" s="22">
-        <v>22227.12</v>
+        <v>59849.63</v>
       </c>
       <c r="D234" s="22">
-        <v>1522.1</v>
+        <v>59849.63</v>
       </c>
       <c r="E234" s="24">
-        <v>0.0685</v>
+        <v>1.0</v>
       </c>
       <c r="F234" s="22">
-        <v>20705.02</v>
+        <v>0.0</v>
       </c>
       <c r="G234" s="24">
-        <v>0.9315</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="235" spans="1:7" ht="17.45">
@@ -8172,23 +8172,23 @@
       </c>
       <c r="B235" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C235" s="22">
-        <v>3680.24</v>
+        <v>22227.12</v>
       </c>
       <c r="D235" s="22">
-        <v>2609.26</v>
+        <v>1522.1</v>
       </c>
       <c r="E235" s="24">
-        <v>0.709</v>
+        <v>0.0685</v>
       </c>
       <c r="F235" s="22">
-        <v>1070.98</v>
+        <v>20705.02</v>
       </c>
       <c r="G235" s="24">
-        <v>0.291</v>
+        <v>0.9315</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="17.45">
@@ -8226,23 +8226,23 @@
       </c>
       <c r="B237" s="21" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C237" s="22">
-        <v>6640.34</v>
+        <v>3680.24</v>
       </c>
       <c r="D237" s="22">
-        <v>1171.13</v>
+        <v>2609.26</v>
       </c>
       <c r="E237" s="24">
-        <v>0.1764</v>
+        <v>0.709</v>
       </c>
       <c r="F237" s="22">
-        <v>5469.21</v>
+        <v>1070.98</v>
       </c>
       <c r="G237" s="24">
-        <v>0.8236</v>
+        <v>0.291</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="17.45">
@@ -8253,23 +8253,23 @@
       </c>
       <c r="B238" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C238" s="22">
-        <v>8487.11</v>
+        <v>6640.34</v>
       </c>
       <c r="D238" s="22">
-        <v>0.0</v>
+        <v>1171.13</v>
       </c>
       <c r="E238" s="24">
-        <v>0.0</v>
+        <v>0.1764</v>
       </c>
       <c r="F238" s="22">
-        <v>8487.11</v>
+        <v>5469.21</v>
       </c>
       <c r="G238" s="24">
-        <v>1.0</v>
+        <v>0.8236</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="17.45">
@@ -8280,23 +8280,23 @@
       </c>
       <c r="B239" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C239" s="22">
-        <v>5149.92</v>
+        <v>8487.11</v>
       </c>
       <c r="D239" s="22">
-        <v>1196.34</v>
+        <v>0.0</v>
       </c>
       <c r="E239" s="24">
-        <v>0.2323</v>
+        <v>0.0</v>
       </c>
       <c r="F239" s="22">
-        <v>3953.58</v>
+        <v>8487.11</v>
       </c>
       <c r="G239" s="24">
-        <v>0.7677</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="17.45">
@@ -8307,50 +8307,50 @@
       </c>
       <c r="B240" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C240" s="22">
-        <v>705.94</v>
+        <v>7174.14</v>
       </c>
       <c r="D240" s="22">
-        <v>31.67</v>
+        <v>3223.71</v>
       </c>
       <c r="E240" s="24">
-        <v>0.0449</v>
+        <v>0.4494</v>
       </c>
       <c r="F240" s="22">
-        <v>674.27</v>
+        <v>3950.43</v>
       </c>
       <c r="G240" s="24">
-        <v>0.9551</v>
+        <v>0.5506</v>
       </c>
     </row>
     <row r="241" spans="1:7" ht="17.45">
       <c r="A241" s="21" t="inlineStr">
         <is>
-          <t>Seamless Stainless Tubes and Pipes - 22</t>
+          <t>Hollow Sections - 21</t>
         </is>
       </c>
       <c r="B241" s="21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C241" s="22">
-        <v>3832.13</v>
+        <v>5149.92</v>
       </c>
       <c r="D241" s="22">
-        <v>3832.13</v>
+        <v>1196.34</v>
       </c>
       <c r="E241" s="24">
-        <v>1.0</v>
+        <v>0.2323</v>
       </c>
       <c r="F241" s="22">
-        <v>0.0</v>
+        <v>3953.58</v>
       </c>
       <c r="G241" s="24">
-        <v>0.0</v>
+        <v>0.7677</v>
       </c>
     </row>
     <row r="242" spans="1:7" ht="17.45">
@@ -8388,23 +8388,23 @@
       </c>
       <c r="B243" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C243" s="22">
-        <v>7174.14</v>
+        <v>705.94</v>
       </c>
       <c r="D243" s="22">
-        <v>3223.71</v>
+        <v>31.67</v>
       </c>
       <c r="E243" s="24">
-        <v>0.4494</v>
+        <v>0.0449</v>
       </c>
       <c r="F243" s="22">
-        <v>3950.43</v>
+        <v>674.27</v>
       </c>
       <c r="G243" s="24">
-        <v>0.5506</v>
+        <v>0.9551</v>
       </c>
     </row>
     <row r="244" spans="1:7" ht="17.45">
@@ -8415,23 +8415,23 @@
       </c>
       <c r="B244" s="21" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C244" s="22">
-        <v>598.03</v>
+        <v>3832.13</v>
       </c>
       <c r="D244" s="22">
-        <v>30.01</v>
+        <v>3832.13</v>
       </c>
       <c r="E244" s="24">
-        <v>0.0502</v>
+        <v>1.0</v>
       </c>
       <c r="F244" s="22">
-        <v>568.02</v>
+        <v>0.0</v>
       </c>
       <c r="G244" s="24">
-        <v>0.9498</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="245" spans="1:7" ht="17.45">
@@ -8442,23 +8442,23 @@
       </c>
       <c r="B245" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="C245" s="22">
-        <v>268.27</v>
+        <v>598.03</v>
       </c>
       <c r="D245" s="22">
-        <v>7.1</v>
+        <v>30.01</v>
       </c>
       <c r="E245" s="24">
-        <v>0.0265</v>
+        <v>0.0502</v>
       </c>
       <c r="F245" s="22">
-        <v>261.17</v>
+        <v>568.02</v>
       </c>
       <c r="G245" s="24">
-        <v>0.9735</v>
+        <v>0.9498</v>
       </c>
     </row>
     <row r="246" spans="1:7" ht="17.45">
@@ -8469,23 +8469,23 @@
       </c>
       <c r="B246" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C246" s="22">
-        <v>512.63</v>
+        <v>774.33</v>
       </c>
       <c r="D246" s="22">
-        <v>0.0</v>
+        <v>232.43</v>
       </c>
       <c r="E246" s="24">
-        <v>0.0</v>
+        <v>0.3002</v>
       </c>
       <c r="F246" s="22">
-        <v>512.63</v>
+        <v>541.9</v>
       </c>
       <c r="G246" s="24">
-        <v>1.0</v>
+        <v>0.6998</v>
       </c>
     </row>
     <row r="247" spans="1:7" ht="17.45">
@@ -8496,23 +8496,23 @@
       </c>
       <c r="B247" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C247" s="22">
-        <v>774.33</v>
+        <v>268.27</v>
       </c>
       <c r="D247" s="22">
-        <v>232.43</v>
+        <v>7.1</v>
       </c>
       <c r="E247" s="24">
-        <v>0.3002</v>
+        <v>0.0265</v>
       </c>
       <c r="F247" s="22">
-        <v>541.9</v>
+        <v>261.17</v>
       </c>
       <c r="G247" s="24">
-        <v>0.6998</v>
+        <v>0.9735</v>
       </c>
     </row>
     <row r="248" spans="1:7" ht="17.45">
@@ -8523,23 +8523,23 @@
       </c>
       <c r="B248" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C248" s="22">
-        <v>446.75</v>
+        <v>512.63</v>
       </c>
       <c r="D248" s="22">
-        <v>24.16</v>
+        <v>0.0</v>
       </c>
       <c r="E248" s="24">
-        <v>0.0541</v>
+        <v>0.0</v>
       </c>
       <c r="F248" s="22">
-        <v>422.59</v>
+        <v>512.63</v>
       </c>
       <c r="G248" s="24">
-        <v>0.9459</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="249" spans="1:7" ht="17.45">
@@ -8550,23 +8550,23 @@
       </c>
       <c r="B249" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C249" s="22">
-        <v>178.57</v>
+        <v>446.75</v>
       </c>
       <c r="D249" s="22">
-        <v>178.57</v>
+        <v>24.16</v>
       </c>
       <c r="E249" s="24">
-        <v>1.0</v>
+        <v>0.0541</v>
       </c>
       <c r="F249" s="22">
-        <v>0.0</v>
+        <v>422.59</v>
       </c>
       <c r="G249" s="24">
-        <v>0.0</v>
+        <v>0.9459</v>
       </c>
     </row>
     <row r="250" spans="1:7" ht="17.45">
@@ -8604,50 +8604,50 @@
       </c>
       <c r="B251" s="21" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C251" s="22">
-        <v>7756.96</v>
+        <v>20167.62</v>
       </c>
       <c r="D251" s="22">
-        <v>842.64</v>
+        <v>2682.54</v>
       </c>
       <c r="E251" s="24">
-        <v>0.1086</v>
+        <v>0.133</v>
       </c>
       <c r="F251" s="22">
-        <v>6914.32</v>
+        <v>17485.08</v>
       </c>
       <c r="G251" s="24">
-        <v>0.8914</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="252" spans="1:7" ht="17.45">
       <c r="A252" s="21" t="inlineStr">
         <is>
-          <t>Other Seamless Tubes - 24</t>
+          <t>Seamless Stainless Tubes and Pipes - 22</t>
         </is>
       </c>
       <c r="B252" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C252" s="22">
-        <v>3052.2</v>
+        <v>178.57</v>
       </c>
       <c r="D252" s="22">
-        <v>0.0</v>
+        <v>178.57</v>
       </c>
       <c r="E252" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F252" s="22">
-        <v>3052.2</v>
+        <v>0.0</v>
       </c>
       <c r="G252" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="17.45">
@@ -8658,23 +8658,23 @@
       </c>
       <c r="B253" s="21" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C253" s="22">
-        <v>20167.62</v>
+        <v>7756.96</v>
       </c>
       <c r="D253" s="22">
-        <v>2682.54</v>
+        <v>842.64</v>
       </c>
       <c r="E253" s="24">
-        <v>0.133</v>
+        <v>0.1086</v>
       </c>
       <c r="F253" s="22">
-        <v>17485.08</v>
+        <v>6914.32</v>
       </c>
       <c r="G253" s="24">
-        <v>0.867</v>
+        <v>0.8914</v>
       </c>
     </row>
     <row r="254" spans="1:7" ht="17.45">
@@ -8685,23 +8685,23 @@
       </c>
       <c r="B254" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C254" s="22">
-        <v>9824.98</v>
+        <v>3052.2</v>
       </c>
       <c r="D254" s="22">
-        <v>1277.5</v>
+        <v>0.0</v>
       </c>
       <c r="E254" s="24">
-        <v>0.13</v>
+        <v>0.0</v>
       </c>
       <c r="F254" s="22">
-        <v>8547.48</v>
+        <v>3052.2</v>
       </c>
       <c r="G254" s="24">
-        <v>0.87</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="17.45">
@@ -8712,23 +8712,23 @@
       </c>
       <c r="B255" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C255" s="22">
-        <v>11895.7</v>
+        <v>1258.1</v>
       </c>
       <c r="D255" s="22">
-        <v>1067.96</v>
+        <v>6.32</v>
       </c>
       <c r="E255" s="24">
-        <v>0.0898</v>
+        <v>0.005</v>
       </c>
       <c r="F255" s="22">
-        <v>10827.74</v>
+        <v>1251.78</v>
       </c>
       <c r="G255" s="24">
-        <v>0.9102</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="256" spans="1:7" ht="17.45">
@@ -8739,23 +8739,23 @@
       </c>
       <c r="B256" s="21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C256" s="22">
-        <v>1258.1</v>
+        <v>9824.98</v>
       </c>
       <c r="D256" s="22">
-        <v>6.32</v>
+        <v>1277.5</v>
       </c>
       <c r="E256" s="24">
-        <v>0.005</v>
+        <v>0.13</v>
       </c>
       <c r="F256" s="22">
-        <v>1251.78</v>
+        <v>8547.48</v>
       </c>
       <c r="G256" s="24">
-        <v>0.995</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="257" spans="1:7" ht="17.45">
@@ -8788,28 +8788,28 @@
     <row r="258" spans="1:7" ht="17.45">
       <c r="A258" s="21" t="inlineStr">
         <is>
-          <t>Large welded tubes - 25.A</t>
+          <t>Other Seamless Tubes - 24</t>
         </is>
       </c>
       <c r="B258" s="21" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C258" s="22">
-        <v>834.24</v>
+        <v>11895.7</v>
       </c>
       <c r="D258" s="22">
-        <v>0.0</v>
+        <v>1067.96</v>
       </c>
       <c r="E258" s="24">
-        <v>0.0</v>
+        <v>0.0898</v>
       </c>
       <c r="F258" s="22">
-        <v>834.24</v>
+        <v>10827.74</v>
       </c>
       <c r="G258" s="24">
-        <v>1.0</v>
+        <v>0.9102</v>
       </c>
     </row>
     <row r="259" spans="1:7" ht="17.45">
@@ -8847,23 +8847,23 @@
       </c>
       <c r="B260" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C260" s="22">
-        <v>662.75</v>
+        <v>834.24</v>
       </c>
       <c r="D260" s="22">
-        <v>13.4</v>
+        <v>0.0</v>
       </c>
       <c r="E260" s="24">
-        <v>0.0202</v>
+        <v>0.0</v>
       </c>
       <c r="F260" s="22">
-        <v>649.35</v>
+        <v>834.24</v>
       </c>
       <c r="G260" s="24">
-        <v>0.9798</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="261" spans="1:7" ht="17.45">
@@ -8874,23 +8874,23 @@
       </c>
       <c r="B261" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C261" s="22">
-        <v>666.56</v>
+        <v>662.75</v>
       </c>
       <c r="D261" s="22">
-        <v>15.27</v>
+        <v>13.4</v>
       </c>
       <c r="E261" s="24">
-        <v>0.0229</v>
+        <v>0.0202</v>
       </c>
       <c r="F261" s="22">
-        <v>651.29</v>
+        <v>649.35</v>
       </c>
       <c r="G261" s="24">
-        <v>0.9771</v>
+        <v>0.9798</v>
       </c>
     </row>
     <row r="262" spans="1:7" ht="17.45">
@@ -8955,11 +8955,11 @@
       </c>
       <c r="B264" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
         </is>
       </c>
       <c r="C264" s="22">
-        <v>584.19</v>
+        <v>13.93</v>
       </c>
       <c r="D264" s="22">
         <v>0.0</v>
@@ -8968,7 +8968,7 @@
         <v>0.0</v>
       </c>
       <c r="F264" s="22">
-        <v>584.19</v>
+        <v>13.93</v>
       </c>
       <c r="G264" s="24">
         <v>1.0</v>
@@ -8977,55 +8977,55 @@
     <row r="265" spans="1:7" ht="17.45">
       <c r="A265" s="21" t="inlineStr">
         <is>
-          <t>Large welded tubes - 25.B</t>
+          <t>Large welded tubes - 25.A</t>
         </is>
       </c>
       <c r="B265" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C265" s="22">
-        <v>10935.66</v>
+        <v>666.56</v>
       </c>
       <c r="D265" s="22">
-        <v>2342.64</v>
+        <v>15.27</v>
       </c>
       <c r="E265" s="24">
-        <v>0.2142</v>
+        <v>0.0229</v>
       </c>
       <c r="F265" s="22">
-        <v>8593.02</v>
+        <v>651.29</v>
       </c>
       <c r="G265" s="24">
-        <v>0.7858</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="266" spans="1:7" ht="17.45">
       <c r="A266" s="21" t="inlineStr">
         <is>
-          <t>Large welded tubes - 25.A</t>
+          <t>Large welded tubes - 25.B</t>
         </is>
       </c>
       <c r="B266" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C266" s="22">
-        <v>13.93</v>
+        <v>10935.66</v>
       </c>
       <c r="D266" s="22">
-        <v>0.0</v>
+        <v>2342.64</v>
       </c>
       <c r="E266" s="24">
-        <v>0.0</v>
+        <v>0.2142</v>
       </c>
       <c r="F266" s="22">
-        <v>13.93</v>
+        <v>8593.02</v>
       </c>
       <c r="G266" s="24">
-        <v>1.0</v>
+        <v>0.7858</v>
       </c>
     </row>
     <row r="267" spans="1:7" ht="17.45">
@@ -9090,23 +9090,23 @@
       </c>
       <c r="B269" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C269" s="22">
-        <v>2029.75</v>
+        <v>2013.16</v>
       </c>
       <c r="D269" s="22">
-        <v>0.0</v>
+        <v>36.31</v>
       </c>
       <c r="E269" s="24">
-        <v>0.0</v>
+        <v>0.018</v>
       </c>
       <c r="F269" s="22">
-        <v>2029.75</v>
+        <v>1976.85</v>
       </c>
       <c r="G269" s="24">
-        <v>1.0</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="270" spans="1:7" ht="17.45">
@@ -9117,23 +9117,23 @@
       </c>
       <c r="B270" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C270" s="22">
-        <v>2013.16</v>
+        <v>2029.75</v>
       </c>
       <c r="D270" s="22">
-        <v>36.31</v>
+        <v>0.0</v>
       </c>
       <c r="E270" s="24">
-        <v>0.018</v>
+        <v>0.0</v>
       </c>
       <c r="F270" s="22">
-        <v>1976.85</v>
+        <v>2029.75</v>
       </c>
       <c r="G270" s="24">
-        <v>0.982</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="271" spans="1:7" ht="17.45">
@@ -9193,82 +9193,82 @@
     <row r="273" spans="1:7" ht="17.45">
       <c r="A273" s="21" t="inlineStr">
         <is>
-          <t>Other Welded Pipes - 26</t>
+          <t>Large welded tubes - 25.B</t>
         </is>
       </c>
       <c r="B273" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C273" s="22">
-        <v>11860.66</v>
+        <v>21.07</v>
       </c>
       <c r="D273" s="22">
-        <v>159.53</v>
+        <v>0.0</v>
       </c>
       <c r="E273" s="24">
-        <v>0.0135</v>
+        <v>0.0</v>
       </c>
       <c r="F273" s="22">
-        <v>11701.13</v>
+        <v>21.07</v>
       </c>
       <c r="G273" s="24">
-        <v>0.9865</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="17.45">
       <c r="A274" s="21" t="inlineStr">
         <is>
-          <t>Large welded tubes - 25.B</t>
+          <t>Other Welded Pipes - 26</t>
         </is>
       </c>
       <c r="B274" s="21" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C274" s="22">
-        <v>21.07</v>
+        <v>22453.26</v>
       </c>
       <c r="D274" s="22">
-        <v>0.0</v>
+        <v>22453.26</v>
       </c>
       <c r="E274" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F274" s="22">
-        <v>21.07</v>
+        <v>0.0</v>
       </c>
       <c r="G274" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="17.45">
       <c r="A275" s="21" t="inlineStr">
         <is>
-          <t>Other Welded Pipes - 26</t>
+          <t>Large welded tubes - 25.A</t>
         </is>
       </c>
       <c r="B275" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C275" s="22">
-        <v>22453.26</v>
+        <v>584.19</v>
       </c>
       <c r="D275" s="22">
-        <v>22453.26</v>
+        <v>0.0</v>
       </c>
       <c r="E275" s="24">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F275" s="22">
-        <v>0.0</v>
+        <v>584.19</v>
       </c>
       <c r="G275" s="24">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="17.45">
@@ -9333,23 +9333,23 @@
       </c>
       <c r="B278" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C278" s="22">
-        <v>4057.59</v>
+        <v>11860.66</v>
       </c>
       <c r="D278" s="22">
-        <v>0.0</v>
+        <v>159.53</v>
       </c>
       <c r="E278" s="24">
-        <v>0.0</v>
+        <v>0.0135</v>
       </c>
       <c r="F278" s="22">
-        <v>4057.59</v>
+        <v>11701.13</v>
       </c>
       <c r="G278" s="24">
-        <v>1.0</v>
+        <v>0.9865</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="17.45">
@@ -9360,23 +9360,23 @@
       </c>
       <c r="B279" s="21" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C279" s="22">
-        <v>1597.91</v>
+        <v>4688.38</v>
       </c>
       <c r="D279" s="22">
-        <v>522.12</v>
+        <v>549.47</v>
       </c>
       <c r="E279" s="24">
-        <v>0.3268</v>
+        <v>0.1172</v>
       </c>
       <c r="F279" s="22">
-        <v>1075.79</v>
+        <v>4138.91</v>
       </c>
       <c r="G279" s="24">
-        <v>0.6732</v>
+        <v>0.8828</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="17.45">
@@ -9387,23 +9387,23 @@
       </c>
       <c r="B280" s="21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C280" s="22">
-        <v>4688.38</v>
+        <v>1597.91</v>
       </c>
       <c r="D280" s="22">
-        <v>549.47</v>
+        <v>522.12</v>
       </c>
       <c r="E280" s="24">
-        <v>0.1172</v>
+        <v>0.3268</v>
       </c>
       <c r="F280" s="22">
-        <v>4138.91</v>
+        <v>1075.79</v>
       </c>
       <c r="G280" s="24">
-        <v>0.8828</v>
+        <v>0.6732</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="17.45">
@@ -9414,23 +9414,23 @@
       </c>
       <c r="B281" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C281" s="22">
-        <v>4282.85</v>
+        <v>4057.59</v>
       </c>
       <c r="D281" s="22">
-        <v>364.67</v>
+        <v>0.0</v>
       </c>
       <c r="E281" s="24">
-        <v>0.0851</v>
+        <v>0.0</v>
       </c>
       <c r="F281" s="22">
-        <v>3918.18</v>
+        <v>4057.59</v>
       </c>
       <c r="G281" s="24">
-        <v>0.9149</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="17.45">
@@ -9441,23 +9441,23 @@
       </c>
       <c r="B282" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C282" s="22">
-        <v>4358.64</v>
+        <v>4282.85</v>
       </c>
       <c r="D282" s="22">
-        <v>514.84</v>
+        <v>364.67</v>
       </c>
       <c r="E282" s="24">
-        <v>0.1181</v>
+        <v>0.0851</v>
       </c>
       <c r="F282" s="22">
-        <v>3843.8</v>
+        <v>3918.18</v>
       </c>
       <c r="G282" s="24">
-        <v>0.8819</v>
+        <v>0.9149</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="17.45">
@@ -9490,28 +9490,28 @@
     <row r="284" spans="1:7" ht="17.45">
       <c r="A284" s="21" t="inlineStr">
         <is>
-          <t>Non-alloy and other alloy cold finished bars - 27</t>
+          <t>Other Welded Pipes - 26</t>
         </is>
       </c>
       <c r="B284" s="21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C284" s="22">
-        <v>3960.92</v>
+        <v>4358.64</v>
       </c>
       <c r="D284" s="22">
-        <v>373.18</v>
+        <v>514.84</v>
       </c>
       <c r="E284" s="24">
-        <v>0.0942</v>
+        <v>0.1181</v>
       </c>
       <c r="F284" s="22">
-        <v>3587.74</v>
+        <v>3843.8</v>
       </c>
       <c r="G284" s="24">
-        <v>0.9058</v>
+        <v>0.8819</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="17.45">
@@ -9522,23 +9522,23 @@
       </c>
       <c r="B285" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C285" s="22">
-        <v>7045.08</v>
+        <v>3960.92</v>
       </c>
       <c r="D285" s="22">
-        <v>519.95</v>
+        <v>373.18</v>
       </c>
       <c r="E285" s="24">
-        <v>0.0738</v>
+        <v>0.0942</v>
       </c>
       <c r="F285" s="22">
-        <v>6525.13</v>
+        <v>3587.74</v>
       </c>
       <c r="G285" s="24">
-        <v>0.9262</v>
+        <v>0.9058</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="17.45">
@@ -9576,23 +9576,23 @@
       </c>
       <c r="B287" s="21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C287" s="22">
-        <v>6054.7</v>
+        <v>7045.08</v>
       </c>
       <c r="D287" s="22">
-        <v>360.57</v>
+        <v>519.95</v>
       </c>
       <c r="E287" s="24">
-        <v>0.0596</v>
+        <v>0.0738</v>
       </c>
       <c r="F287" s="22">
-        <v>5694.13</v>
+        <v>6525.13</v>
       </c>
       <c r="G287" s="24">
-        <v>0.9404</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="17.45">
@@ -9603,23 +9603,23 @@
       </c>
       <c r="B288" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C288" s="22">
-        <v>2222.43</v>
+        <v>6054.7</v>
       </c>
       <c r="D288" s="22">
-        <v>0.45</v>
+        <v>360.57</v>
       </c>
       <c r="E288" s="24">
-        <v>0.0002</v>
+        <v>0.0596</v>
       </c>
       <c r="F288" s="22">
-        <v>2221.98</v>
+        <v>5694.13</v>
       </c>
       <c r="G288" s="24">
-        <v>0.9998</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="17.45">
@@ -9630,23 +9630,23 @@
       </c>
       <c r="B289" s="21" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C289" s="22">
-        <v>1715.77</v>
+        <v>1838.58</v>
       </c>
       <c r="D289" s="22">
-        <v>62.96</v>
+        <v>175.76</v>
       </c>
       <c r="E289" s="24">
-        <v>0.0367</v>
+        <v>0.0956</v>
       </c>
       <c r="F289" s="22">
-        <v>1652.81</v>
+        <v>1662.82</v>
       </c>
       <c r="G289" s="24">
-        <v>0.9633</v>
+        <v>0.9044</v>
       </c>
     </row>
     <row r="290" spans="1:7" ht="17.45">
@@ -9657,23 +9657,23 @@
       </c>
       <c r="B290" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C290" s="22">
-        <v>1838.58</v>
+        <v>1715.77</v>
       </c>
       <c r="D290" s="22">
-        <v>175.76</v>
+        <v>62.96</v>
       </c>
       <c r="E290" s="24">
-        <v>0.0956</v>
+        <v>0.0367</v>
       </c>
       <c r="F290" s="22">
-        <v>1662.82</v>
+        <v>1652.81</v>
       </c>
       <c r="G290" s="24">
-        <v>0.9044</v>
+        <v>0.9633</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="17.45">
@@ -9706,28 +9706,28 @@
     <row r="292" spans="1:7" ht="17.45">
       <c r="A292" s="21" t="inlineStr">
         <is>
-          <t>Non Alloy Wire - 28</t>
+          <t>Non-alloy and other alloy cold finished bars - 27</t>
         </is>
       </c>
       <c r="B292" s="21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>FTA Quota – Other countries</t>
         </is>
       </c>
       <c r="C292" s="22">
-        <v>24235.3</v>
+        <v>2222.43</v>
       </c>
       <c r="D292" s="22">
-        <v>2745.72</v>
+        <v>0.45</v>
       </c>
       <c r="E292" s="24">
-        <v>0.1133</v>
+        <v>0.0002</v>
       </c>
       <c r="F292" s="22">
-        <v>21489.58</v>
+        <v>2221.98</v>
       </c>
       <c r="G292" s="24">
-        <v>0.8867</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="17.45">
@@ -9738,23 +9738,23 @@
       </c>
       <c r="B293" s="21" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C293" s="22">
-        <v>20689.52</v>
+        <v>24235.3</v>
       </c>
       <c r="D293" s="22">
-        <v>1188.24</v>
+        <v>2745.72</v>
       </c>
       <c r="E293" s="24">
-        <v>0.0574</v>
+        <v>0.1133</v>
       </c>
       <c r="F293" s="22">
-        <v>19501.28</v>
+        <v>21489.58</v>
       </c>
       <c r="G293" s="24">
-        <v>0.9426</v>
+        <v>0.8867</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="17.45">
@@ -9765,23 +9765,23 @@
       </c>
       <c r="B294" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – Other countries</t>
+          <t>FTA Quota – CSQ</t>
         </is>
       </c>
       <c r="C294" s="22">
-        <v>8489.22</v>
+        <v>4496.4</v>
       </c>
       <c r="D294" s="22">
-        <v>12.44</v>
+        <v>0.0</v>
       </c>
       <c r="E294" s="24">
-        <v>0.0015</v>
+        <v>0.0</v>
       </c>
       <c r="F294" s="22">
-        <v>8476.78</v>
+        <v>4496.4</v>
       </c>
       <c r="G294" s="24">
-        <v>0.9985</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="295" spans="1:7" ht="17.45">
@@ -9792,23 +9792,23 @@
       </c>
       <c r="B295" s="21" t="inlineStr">
         <is>
-          <t>Other countries</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C295" s="22">
-        <v>7072.28</v>
+        <v>20689.52</v>
       </c>
       <c r="D295" s="22">
-        <v>877.86</v>
+        <v>1188.24</v>
       </c>
       <c r="E295" s="24">
-        <v>0.1241</v>
+        <v>0.0574</v>
       </c>
       <c r="F295" s="22">
-        <v>6194.42</v>
+        <v>19501.28</v>
       </c>
       <c r="G295" s="24">
-        <v>0.8759</v>
+        <v>0.9426</v>
       </c>
     </row>
     <row r="296" spans="1:7" ht="17.45">
@@ -9819,23 +9819,23 @@
       </c>
       <c r="B296" s="21" t="inlineStr">
         <is>
-          <t>FTA Quota – CSQ</t>
+          <t>Other countries</t>
         </is>
       </c>
       <c r="C296" s="22">
-        <v>4496.4</v>
+        <v>7072.28</v>
       </c>
       <c r="D296" s="22">
-        <v>0.0</v>
+        <v>877.86</v>
       </c>
       <c r="E296" s="24">
-        <v>0.0</v>
+        <v>0.1241</v>
       </c>
       <c r="F296" s="22">
-        <v>4496.4</v>
+        <v>6194.42</v>
       </c>
       <c r="G296" s="24">
-        <v>1.0</v>
+        <v>0.8759</v>
       </c>
     </row>
     <row r="297" spans="1:7" ht="17.45">
@@ -9846,29 +9846,56 @@
       </c>
       <c r="B297" s="21" t="inlineStr">
         <is>
+          <t>FTA Quota – Other countries</t>
+        </is>
+      </c>
+      <c r="C297" s="22">
+        <v>8489.22</v>
+      </c>
+      <c r="D297" s="22">
+        <v>12.44</v>
+      </c>
+      <c r="E297" s="24">
+        <v>0.0015</v>
+      </c>
+      <c r="F297" s="22">
+        <v>8476.78</v>
+      </c>
+      <c r="G297" s="24">
+        <v>0.9985</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" ht="17.45">
+      <c r="A298" s="21" t="inlineStr">
+        <is>
+          <t>Non Alloy Wire - 28</t>
+        </is>
+      </c>
+      <c r="B298" s="21" t="inlineStr">
+        <is>
           <t>United Kingdom (to Northern Ireland from other parts of the United Kingdom)</t>
         </is>
       </c>
-      <c r="C297" s="22">
+      <c r="C298" s="22">
         <v>190.57</v>
       </c>
-      <c r="D297" s="22">
-        <v>0.0</v>
-      </c>
-      <c r="E297" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="F297" s="22">
+      <c r="D298" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="E298" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="F298" s="22">
         <v>190.57</v>
       </c>
-      <c r="G297" s="24">
+      <c r="G298" s="24">
         <v>1.0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
   <protectedRanges>
-    <protectedRange sqref="A15:G297" name="Range1"/>
+    <protectedRange sqref="A15:G298" name="Range1"/>
   </protectedRanges>
   <mergeCells count="1">
     <mergeCell ref="D5:G14"/>
